--- a/Data/cleaned/Car_sales.xlsx
+++ b/Data/cleaned/Car_sales.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Car-Sales-Analysis\data\cleaned\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D03156E2-A754-4C2A-9D82-E124E672BB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40955B82-7AA1-4641-8A45-1120686DD148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{43647843-1222-4844-9DE2-3FFA0F7681EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Car_sales" sheetId="1" r:id="rId1"/>
-    <sheet name="Car_sales (2)" sheetId="3" r:id="rId2"/>
+    <sheet name="Car_sales_Cleaned" sheetId="3" r:id="rId2"/>
+    <sheet name="Cleaning_Log" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Car_sales!$A$1:$P$158</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Car_sales (2)'!$A$1:$P$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Car_sales_Cleaned!$A$1:$P$158</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="208">
   <si>
     <t>Manufacturer</t>
   </si>
@@ -667,7 +668,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1152,7 +1153,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1178,11 +1179,17 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1539,7 +1546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85E8AC9A-639B-4E81-9DF9-598A3E709EBB}">
-  <dimension ref="A1:P158"/>
+  <dimension ref="A1:V158"/>
   <sheetFormatPr defaultColWidth="18.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="18.77734375" style="1"/>
@@ -1711,6 +1718,7 @@
       <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="F4" s="5"/>
       <c r="G4" s="1">
         <v>3.2</v>
       </c>
@@ -1738,6 +1746,7 @@
       <c r="O4" s="3">
         <v>40912</v>
       </c>
+      <c r="P4" s="5"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1949,6 +1958,7 @@
       <c r="C9" s="1">
         <v>19.747</v>
       </c>
+      <c r="D9" s="5"/>
       <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
@@ -2336,7 +2346,7 @@
         <v>113.85459760000001</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>35</v>
       </c>
@@ -2370,6 +2380,7 @@
       <c r="K17" s="1">
         <v>201</v>
       </c>
+      <c r="L17" s="5"/>
       <c r="M17" s="1">
         <v>18.5</v>
       </c>
@@ -2383,7 +2394,7 @@
         <v>115.6213578</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -2433,7 +2444,7 @@
         <v>113.7658739</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
@@ -2483,7 +2494,7 @@
         <v>83.483093580000002</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>35</v>
       </c>
@@ -2493,6 +2504,7 @@
       <c r="C20" s="1">
         <v>14.785</v>
       </c>
+      <c r="D20" s="5"/>
       <c r="E20" s="1" t="s">
         <v>41</v>
       </c>
@@ -2530,7 +2542,7 @@
         <v>109.5091165</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
@@ -2580,7 +2592,7 @@
         <v>46.363347470000001</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
@@ -2630,7 +2642,7 @@
         <v>67.314462160000005</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
@@ -2679,8 +2691,17 @@
       <c r="P23" s="1">
         <v>69.991395600000004</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R23" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="S23" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
+      <c r="V23"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>42</v>
       </c>
@@ -2729,8 +2750,17 @@
       <c r="P24" s="1">
         <v>72.030917189999997</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R24" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="S24" s="6">
+        <v>36</v>
+      </c>
+      <c r="T24" s="12"/>
+      <c r="U24" s="8"/>
+      <c r="V24"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -2779,8 +2809,17 @@
       <c r="P25" s="1">
         <v>81.118543329999994</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R25" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="S25" s="6">
+        <v>2</v>
+      </c>
+      <c r="T25" s="12"/>
+      <c r="U25" s="12"/>
+      <c r="V25"/>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
@@ -2829,8 +2868,17 @@
       <c r="P26" s="1">
         <v>141.14115000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R26" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="S26" s="6">
+        <v>1</v>
+      </c>
+      <c r="T26" s="12"/>
+      <c r="U26" s="8"/>
+      <c r="V26"/>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
@@ -2879,8 +2927,17 @@
       <c r="P27" s="1">
         <v>48.297636099999998</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R27" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="S27" s="6">
+        <v>1</v>
+      </c>
+      <c r="T27" s="12"/>
+      <c r="U27" s="8"/>
+      <c r="V27"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
@@ -2929,8 +2986,17 @@
       <c r="P28" s="1">
         <v>23.276272330000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R28" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="S28" s="6">
+        <v>1</v>
+      </c>
+      <c r="T28" s="12"/>
+      <c r="U28" s="8"/>
+      <c r="V28"/>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>42</v>
       </c>
@@ -2940,6 +3006,7 @@
       <c r="C29" s="1">
         <v>107.995</v>
       </c>
+      <c r="D29" s="5"/>
       <c r="E29" s="1" t="s">
         <v>18</v>
       </c>
@@ -2976,8 +3043,17 @@
       <c r="P29" s="1">
         <v>71.838039440000003</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R29" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="S29" s="6">
+        <v>1</v>
+      </c>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8"/>
+      <c r="V29"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>52</v>
       </c>
@@ -3026,8 +3102,17 @@
       <c r="P30" s="1">
         <v>65.957183959999995</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R30" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="S30" s="6">
+        <v>1</v>
+      </c>
+      <c r="T30" s="12"/>
+      <c r="U30" s="8"/>
+      <c r="V30"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>52</v>
       </c>
@@ -3076,8 +3161,17 @@
       <c r="P31" s="1">
         <v>69.521355049999997</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R31" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="S31" s="6">
+        <v>2</v>
+      </c>
+      <c r="T31" s="12"/>
+      <c r="U31" s="8"/>
+      <c r="V31"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>52</v>
       </c>
@@ -3126,8 +3220,17 @@
       <c r="P32" s="1">
         <v>80.02378204</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="S32" s="6">
+        <v>1</v>
+      </c>
+      <c r="T32" s="12"/>
+      <c r="U32" s="8"/>
+      <c r="V32"/>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
@@ -3176,8 +3279,17 @@
       <c r="P33" s="1">
         <v>53.566199869999998</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R33" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="S33" s="6">
+        <v>3</v>
+      </c>
+      <c r="T33" s="12"/>
+      <c r="U33" s="8"/>
+      <c r="V33"/>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>52</v>
       </c>
@@ -3226,8 +3338,17 @@
       <c r="P34" s="1">
         <v>101.3292807</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R34" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="S34" s="6">
+        <v>0</v>
+      </c>
+      <c r="T34" s="8"/>
+      <c r="U34" s="8"/>
+      <c r="V34"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>52</v>
       </c>
@@ -3243,11 +3364,30 @@
       <c r="E35" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
       <c r="O35" s="3">
         <v>40737</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P35" s="5"/>
+      <c r="R35" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="S35" s="6">
+        <v>2</v>
+      </c>
+      <c r="T35" s="12"/>
+      <c r="U35" s="12"/>
+      <c r="V35"/>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>52</v>
       </c>
@@ -3257,6 +3397,7 @@
       <c r="C36" s="1">
         <v>30.696000000000002</v>
       </c>
+      <c r="D36" s="5"/>
       <c r="E36" s="1" t="s">
         <v>18</v>
       </c>
@@ -3293,8 +3434,12 @@
       <c r="P36" s="1">
         <v>101.6552441</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R36"/>
+      <c r="T36"/>
+      <c r="U36"/>
+      <c r="V36"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>60</v>
       </c>
@@ -3343,8 +3488,11 @@
       <c r="P37" s="1">
         <v>52.084898750000001</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="T37"/>
+      <c r="U37"/>
+      <c r="V37"/>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>60</v>
       </c>
@@ -3393,8 +3541,17 @@
       <c r="P38" s="1">
         <v>65.650508340000002</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R38" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="S38" s="8">
+        <v>51</v>
+      </c>
+      <c r="T38"/>
+      <c r="U38"/>
+      <c r="V38"/>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>60</v>
       </c>
@@ -3444,7 +3601,7 @@
         <v>67.876107840000003</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>60</v>
       </c>
@@ -3484,6 +3641,7 @@
       <c r="M40" s="1">
         <v>17</v>
       </c>
+      <c r="N40" s="5"/>
       <c r="O40" s="3">
         <v>41062</v>
       </c>
@@ -3491,7 +3649,7 @@
         <v>80.831470170000003</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>60</v>
       </c>
@@ -3541,7 +3699,7 @@
         <v>188.14432300000001</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>60</v>
       </c>
@@ -3591,7 +3749,7 @@
         <v>90.211700050000005</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>60</v>
       </c>
@@ -3641,7 +3799,7 @@
         <v>71.135291609999996</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>60</v>
       </c>
@@ -3691,7 +3849,7 @@
         <v>70.078321540000005</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>60</v>
       </c>
@@ -3741,7 +3899,7 @@
         <v>49.64500177</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>60</v>
       </c>
@@ -3751,6 +3909,7 @@
       <c r="C46" s="1">
         <v>101.32299999999999</v>
       </c>
+      <c r="D46" s="5"/>
       <c r="E46" s="1" t="s">
         <v>41</v>
       </c>
@@ -3788,7 +3947,7 @@
         <v>92.85412522</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>60</v>
       </c>
@@ -3838,7 +3997,7 @@
         <v>61.227000310000001</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>72</v>
       </c>
@@ -4048,6 +4207,7 @@
       <c r="C52" s="1">
         <v>175.67</v>
       </c>
+      <c r="D52" s="5"/>
       <c r="E52" s="1" t="s">
         <v>18</v>
       </c>
@@ -4845,6 +5005,7 @@
       <c r="C68" s="1">
         <v>15.467000000000001</v>
       </c>
+      <c r="D68" s="5"/>
       <c r="E68" s="1" t="s">
         <v>18</v>
       </c>
@@ -5142,6 +5303,7 @@
       <c r="C74" s="1">
         <v>3.3340000000000001</v>
       </c>
+      <c r="D74" s="5"/>
       <c r="E74" s="1" t="s">
         <v>18</v>
       </c>
@@ -5239,6 +5401,7 @@
       <c r="C76" s="1">
         <v>9.1259999999999994</v>
       </c>
+      <c r="D76" s="5"/>
       <c r="E76" s="1" t="s">
         <v>41</v>
       </c>
@@ -5286,6 +5449,7 @@
       <c r="C77" s="1">
         <v>51.238</v>
       </c>
+      <c r="D77" s="5"/>
       <c r="E77" s="1" t="s">
         <v>41</v>
       </c>
@@ -5433,6 +5597,7 @@
       <c r="C80" s="1">
         <v>22.925000000000001</v>
       </c>
+      <c r="D80" s="5"/>
       <c r="E80" s="1" t="s">
         <v>41</v>
       </c>
@@ -6330,6 +6495,7 @@
       <c r="C98" s="1">
         <v>7.9980000000000002</v>
       </c>
+      <c r="D98" s="5"/>
       <c r="E98" s="1" t="s">
         <v>18</v>
       </c>
@@ -6377,6 +6543,7 @@
       <c r="C99" s="1">
         <v>1.526</v>
       </c>
+      <c r="D99" s="5"/>
       <c r="E99" s="1" t="s">
         <v>18</v>
       </c>
@@ -6424,6 +6591,7 @@
       <c r="C100" s="1">
         <v>11.592000000000001</v>
       </c>
+      <c r="D100" s="5"/>
       <c r="E100" s="1" t="s">
         <v>18</v>
       </c>
@@ -6471,6 +6639,7 @@
       <c r="C101" s="1">
         <v>0.95399999999999996</v>
       </c>
+      <c r="D101" s="5"/>
       <c r="E101" s="1" t="s">
         <v>18</v>
       </c>
@@ -6518,6 +6687,7 @@
       <c r="C102" s="1">
         <v>28.975999999999999</v>
       </c>
+      <c r="D102" s="5"/>
       <c r="E102" s="1" t="s">
         <v>41</v>
       </c>
@@ -6815,6 +6985,7 @@
       <c r="C108" s="1">
         <v>54.158000000000001</v>
       </c>
+      <c r="D108" s="5"/>
       <c r="E108" s="1" t="s">
         <v>41</v>
       </c>
@@ -6862,6 +7033,7 @@
       <c r="C109" s="1">
         <v>65.004999999999995</v>
       </c>
+      <c r="D109" s="5"/>
       <c r="E109" s="1" t="s">
         <v>41</v>
       </c>
@@ -6959,6 +7131,7 @@
       <c r="C111" s="1">
         <v>38.554000000000002</v>
       </c>
+      <c r="D111" s="5"/>
       <c r="E111" s="1" t="s">
         <v>18</v>
       </c>
@@ -6986,6 +7159,7 @@
       <c r="M111" s="1">
         <v>18</v>
       </c>
+      <c r="N111" s="5"/>
       <c r="O111" s="3">
         <v>40634</v>
       </c>
@@ -7003,6 +7177,7 @@
       <c r="C112" s="1">
         <v>80.254999999999995</v>
       </c>
+      <c r="D112" s="5"/>
       <c r="E112" s="1" t="s">
         <v>18</v>
       </c>
@@ -7350,6 +7525,7 @@
       <c r="C119" s="1">
         <v>1.8720000000000001</v>
       </c>
+      <c r="D119" s="5"/>
       <c r="E119" s="1" t="s">
         <v>18</v>
       </c>
@@ -7647,6 +7823,7 @@
       <c r="C125" s="1">
         <v>39.572000000000003</v>
       </c>
+      <c r="D125" s="5"/>
       <c r="E125" s="1" t="s">
         <v>41</v>
       </c>
@@ -7844,6 +8021,7 @@
       <c r="C129" s="1">
         <v>9.1910000000000007</v>
       </c>
+      <c r="D129" s="5"/>
       <c r="E129" s="1" t="s">
         <v>18</v>
       </c>
@@ -7891,6 +8069,7 @@
       <c r="C130" s="1">
         <v>12.115</v>
       </c>
+      <c r="D130" s="5"/>
       <c r="E130" s="1" t="s">
         <v>18</v>
       </c>
@@ -8088,6 +8267,7 @@
       <c r="C134" s="1">
         <v>8.4719999999999995</v>
       </c>
+      <c r="D134" s="5"/>
       <c r="E134" s="1" t="s">
         <v>18</v>
       </c>
@@ -8135,6 +8315,7 @@
       <c r="C135" s="1">
         <v>49.988999999999997</v>
       </c>
+      <c r="D135" s="5"/>
       <c r="E135" s="1" t="s">
         <v>18</v>
       </c>
@@ -8182,6 +8363,7 @@
       <c r="C136" s="1">
         <v>47.106999999999999</v>
       </c>
+      <c r="D136" s="5"/>
       <c r="E136" s="1" t="s">
         <v>18</v>
       </c>
@@ -8229,6 +8411,7 @@
       <c r="C137" s="1">
         <v>33.027999999999999</v>
       </c>
+      <c r="D137" s="5"/>
       <c r="E137" s="1" t="s">
         <v>41</v>
       </c>
@@ -8526,6 +8709,7 @@
       <c r="C143" s="1">
         <v>65.119</v>
       </c>
+      <c r="D143" s="5"/>
       <c r="E143" s="1" t="s">
         <v>41</v>
       </c>
@@ -8973,6 +9157,7 @@
       <c r="C152" s="1">
         <v>49.463000000000001</v>
       </c>
+      <c r="D152" s="5"/>
       <c r="E152" s="1" t="s">
         <v>18</v>
       </c>
@@ -9020,6 +9205,7 @@
       <c r="C153" s="1">
         <v>16.957000000000001</v>
       </c>
+      <c r="D153" s="5"/>
       <c r="E153" s="1" t="s">
         <v>18</v>
       </c>
@@ -9067,6 +9253,7 @@
       <c r="C154" s="1">
         <v>3.5449999999999999</v>
       </c>
+      <c r="D154" s="5"/>
       <c r="E154" s="1" t="s">
         <v>18</v>
       </c>
@@ -9114,6 +9301,7 @@
       <c r="C155" s="1">
         <v>15.244999999999999</v>
       </c>
+      <c r="D155" s="5"/>
       <c r="E155" s="1" t="s">
         <v>18</v>
       </c>
@@ -9161,6 +9349,7 @@
       <c r="C156" s="1">
         <v>17.530999999999999</v>
       </c>
+      <c r="D156" s="5"/>
       <c r="E156" s="1" t="s">
         <v>18</v>
       </c>
@@ -9208,6 +9397,7 @@
       <c r="C157" s="1">
         <v>3.4929999999999999</v>
       </c>
+      <c r="D157" s="5"/>
       <c r="E157" s="1" t="s">
         <v>18</v>
       </c>
@@ -9255,6 +9445,7 @@
       <c r="C158" s="1">
         <v>18.969000000000001</v>
       </c>
+      <c r="D158" s="5"/>
       <c r="E158" s="1" t="s">
         <v>18</v>
       </c>
@@ -9362,10 +9553,10 @@
       <c r="B2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="7">
         <v>16.919</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="7">
         <v>16.36</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -9401,7 +9592,7 @@
       <c r="O2" s="3">
         <v>40941</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="7">
         <v>58.280149520000002</v>
       </c>
     </row>
@@ -9412,10 +9603,10 @@
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="7">
         <v>39.384</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="7">
         <v>19.875</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -9451,7 +9642,7 @@
       <c r="O3" s="3">
         <v>40697</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="7">
         <v>91.370777660000002</v>
       </c>
     </row>
@@ -9462,16 +9653,19 @@
       <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="7">
         <v>14.114000000000001</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="7">
         <v>18.225000000000001</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="11">
+        <f>22.8</f>
+        <v>22.8</v>
+      </c>
       <c r="G4" s="1">
         <v>3.2</v>
       </c>
@@ -9499,7 +9693,10 @@
       <c r="O4" s="3">
         <v>40912</v>
       </c>
-      <c r="P4" s="5"/>
+      <c r="P4" s="11">
+        <f>72.03</f>
+        <v>72.03</v>
+      </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -9508,10 +9705,10 @@
       <c r="B5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="7">
         <v>8.5879999999999992</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="7">
         <v>29.725000000000001</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -9547,7 +9744,7 @@
       <c r="O5" s="3">
         <v>40612</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="7">
         <v>91.389779329999996</v>
       </c>
       <c r="R5" s="8" t="s">
@@ -9555,7 +9752,7 @@
       </c>
       <c r="S5" s="8">
         <f>COUNTBLANK(A1:P158)</f>
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
@@ -9565,10 +9762,10 @@
       <c r="B6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="7">
         <v>20.396999999999998</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="7">
         <v>22.254999999999999</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -9604,7 +9801,7 @@
       <c r="O6" s="3">
         <v>40824</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="7">
         <v>62.777639200000003</v>
       </c>
     </row>
@@ -9615,10 +9812,10 @@
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="7">
         <v>18.78</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="7">
         <v>23.555</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -9654,7 +9851,7 @@
       <c r="O7" s="3">
         <v>40764</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="7">
         <v>84.565105020000004</v>
       </c>
       <c r="R7" s="6" t="s">
@@ -9677,10 +9874,10 @@
       <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="7">
         <v>1.38</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="7">
         <v>39</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -9716,7 +9913,7 @@
       <c r="O8" s="3">
         <v>40966</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="7">
         <v>134.65685819999999</v>
       </c>
       <c r="R8" s="10" t="s">
@@ -9724,15 +9921,15 @@
       </c>
       <c r="S8" s="6">
         <f>COUNTBLANK(D1:D158)</f>
-        <v>36</v>
-      </c>
-      <c r="T8" s="7">
+        <v>0</v>
+      </c>
+      <c r="T8" s="12">
         <f>AVERAGE(D2:D158)</f>
-        <v>18.072975206611574</v>
-      </c>
-      <c r="U8" s="1">
-        <f>MEDIAN(D2:D159)</f>
-        <v>14.18</v>
+        <v>18.6691719745223</v>
+      </c>
+      <c r="U8" s="8">
+        <f>MEDIAN(D2:D158)</f>
+        <v>14.875</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
@@ -9742,10 +9939,13 @@
       <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="7">
         <v>19.747</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="11">
+        <f>Car_sales_Cleaned!D2</f>
+        <v>16.36</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
@@ -9779,7 +9979,7 @@
       <c r="O9" s="3">
         <v>40722</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="7">
         <v>71.191206710000003</v>
       </c>
       <c r="R9" s="10" t="s">
@@ -9787,15 +9987,15 @@
       </c>
       <c r="S9" s="6">
         <f>COUNTBLANK(F1:F158)</f>
-        <v>2</v>
-      </c>
-      <c r="T9" s="1">
-        <f>AVERAGE(D2:D158)</f>
-        <v>18.072975206611574</v>
-      </c>
-      <c r="U9" s="1">
-        <f t="shared" ref="U9:U19" si="0">MEDIAN(D3:D160)</f>
-        <v>14.094999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="T9" s="12">
+        <f>AVERAGE(F1:F158)</f>
+        <v>27.332273885350293</v>
+      </c>
+      <c r="U9" s="12">
+        <f>MEDIAN(F2:F158)</f>
+        <v>22.8</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
@@ -9805,10 +10005,10 @@
       <c r="B10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="7">
         <v>9.2309999999999999</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="7">
         <v>28.675000000000001</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -9844,7 +10044,7 @@
       <c r="O10" s="3">
         <v>40937</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="7">
         <v>81.877068559999998</v>
       </c>
       <c r="R10" s="10" t="s">
@@ -9852,15 +10052,15 @@
       </c>
       <c r="S10" s="6">
         <f>COUNTBLANK(G1:G158)</f>
-        <v>1</v>
-      </c>
-      <c r="T10" s="1">
-        <f t="shared" ref="T10:T19" si="1">AVERAGE(D3:D159)</f>
-        <v>18.087250000000001</v>
-      </c>
-      <c r="U10" s="1">
-        <f t="shared" si="0"/>
-        <v>14.01</v>
+        <v>0</v>
+      </c>
+      <c r="T10" s="12">
+        <f>AVERAGE(G1:G158)</f>
+        <v>3.060509554140125</v>
+      </c>
+      <c r="U10" s="8">
+        <f>MEDIAN(G2:G158)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
@@ -9870,10 +10070,10 @@
       <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="7">
         <v>17.527000000000001</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="7">
         <v>36.125</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -9909,7 +10109,7 @@
       <c r="O11" s="3">
         <v>40637</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="7">
         <v>83.998723799999993</v>
       </c>
       <c r="R11" s="10" t="s">
@@ -9917,15 +10117,15 @@
       </c>
       <c r="S11" s="6">
         <f>COUNTBLANK(H1:H158)</f>
-        <v>1</v>
-      </c>
-      <c r="T11" s="1">
-        <f t="shared" si="1"/>
-        <v>18.072226890756305</v>
-      </c>
-      <c r="U11" s="1">
-        <f t="shared" si="0"/>
-        <v>13.95</v>
+        <v>0</v>
+      </c>
+      <c r="T11" s="12">
+        <f>AVERAGE(H1:H158)</f>
+        <v>185.89490445859872</v>
+      </c>
+      <c r="U11" s="8">
+        <f>MEDIAN(H2:H158)</f>
+        <v>177.5</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
@@ -9935,10 +10135,10 @@
       <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="7">
         <v>91.561000000000007</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="7">
         <v>12.475</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -9974,7 +10174,7 @@
       <c r="O12" s="3">
         <v>40849</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="7">
         <v>71.181451319999994</v>
       </c>
       <c r="R12" s="10" t="s">
@@ -9982,15 +10182,15 @@
       </c>
       <c r="S12" s="6">
         <f>COUNTBLANK(I1:I158)</f>
-        <v>1</v>
-      </c>
-      <c r="T12" s="1">
-        <f t="shared" si="1"/>
-        <v>18.070932203389834</v>
-      </c>
-      <c r="U12" s="1">
-        <f t="shared" si="0"/>
-        <v>13.89</v>
+        <v>0</v>
+      </c>
+      <c r="T12" s="12">
+        <f>AVERAGE(I1:I158)</f>
+        <v>107.48407643312102</v>
+      </c>
+      <c r="U12" s="8">
+        <f>MEDIAN(I2:I158)</f>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
@@ -10000,10 +10200,10 @@
       <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="7">
         <v>39.35</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="7">
         <v>13.74</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -10039,7 +10239,7 @@
       <c r="O13" s="3">
         <v>40789</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="7">
         <v>95.636702529999994</v>
       </c>
       <c r="R13" s="10" t="s">
@@ -10047,15 +10247,15 @@
       </c>
       <c r="S13" s="6">
         <f>COUNTBLANK(J1:J158)</f>
-        <v>1</v>
-      </c>
-      <c r="T13" s="1">
-        <f t="shared" si="1"/>
-        <v>17.971324786324789</v>
-      </c>
-      <c r="U13" s="1">
-        <f t="shared" si="0"/>
-        <v>13.885000000000002</v>
+        <v>0</v>
+      </c>
+      <c r="T13" s="8">
+        <f>AVERAGE(J1:J158)</f>
+        <v>71.146178343949018</v>
+      </c>
+      <c r="U13" s="8">
+        <f>MEDIAN(J2:J158)</f>
+        <v>70.55</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
@@ -10065,10 +10265,10 @@
       <c r="B14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="7">
         <v>27.850999999999999</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="7">
         <v>20.190000000000001</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -10104,7 +10304,7 @@
       <c r="O14" s="3">
         <v>40991</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="7">
         <v>85.828408249999995</v>
       </c>
       <c r="R14" s="10" t="s">
@@ -10112,15 +10312,15 @@
       </c>
       <c r="S14" s="6">
         <f>COUNTBLANK(K1:K158)</f>
-        <v>1</v>
-      </c>
-      <c r="T14" s="1">
-        <f t="shared" si="1"/>
-        <v>17.934396551724145</v>
-      </c>
-      <c r="U14" s="1">
-        <f t="shared" si="0"/>
-        <v>13.88</v>
+        <v>0</v>
+      </c>
+      <c r="T14" s="12">
+        <f>AVERAGE(K1:K158)</f>
+        <v>187.34713375796184</v>
+      </c>
+      <c r="U14" s="8">
+        <f>MEDIAN(K2:K158)</f>
+        <v>187.9</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
@@ -10130,10 +10330,10 @@
       <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="7">
         <v>83.257000000000005</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="7">
         <v>13.36</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -10169,7 +10369,7 @@
       <c r="O15" s="3">
         <v>40747</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="7">
         <v>84.254525810000004</v>
       </c>
       <c r="R15" s="10" t="s">
@@ -10177,15 +10377,15 @@
       </c>
       <c r="S15" s="6">
         <f>COUNTBLANK(L1:L158)</f>
-        <v>2</v>
-      </c>
-      <c r="T15" s="1">
-        <f t="shared" si="1"/>
-        <v>17.885521739130439</v>
-      </c>
-      <c r="U15" s="1">
-        <f t="shared" si="0"/>
-        <v>13.835000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="T15" s="12">
+        <f>AVERAGE(L1:L158)</f>
+        <v>3.3775668789808919</v>
+      </c>
+      <c r="U15" s="8">
+        <f>MEDIAN(L2:L158)</f>
+        <v>3.3420000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
@@ -10195,10 +10395,10 @@
       <c r="B16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="7">
         <v>63.728999999999999</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="7">
         <v>22.524999999999999</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -10234,7 +10434,7 @@
       <c r="O16" s="3">
         <v>40962</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="7">
         <v>113.85459760000001</v>
       </c>
       <c r="R16" s="10" t="s">
@@ -10242,15 +10442,15 @@
       </c>
       <c r="S16" s="6">
         <f>COUNTBLANK(M1:M158)</f>
-        <v>1</v>
-      </c>
-      <c r="T16" s="1">
-        <f t="shared" si="1"/>
-        <v>17.700307017543864</v>
-      </c>
-      <c r="U16" s="1">
-        <f t="shared" si="0"/>
-        <v>13.835000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="T16" s="12">
+        <f>AVERAGE(M1:M158)</f>
+        <v>17.947133757961787</v>
+      </c>
+      <c r="U16" s="8">
+        <f>MEDIAN(M2:M158)</f>
+        <v>17.2</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
@@ -10260,10 +10460,10 @@
       <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="7">
         <v>15.943</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="7">
         <v>27.1</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -10287,7 +10487,10 @@
       <c r="K17" s="1">
         <v>201</v>
       </c>
-      <c r="L17" s="5"/>
+      <c r="L17" s="5">
+        <f>3.342</f>
+        <v>3.3420000000000001</v>
+      </c>
       <c r="M17" s="1">
         <v>18.5</v>
       </c>
@@ -10297,7 +10500,7 @@
       <c r="O17" s="3">
         <v>40662</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="7">
         <v>115.6213578</v>
       </c>
       <c r="R17" s="10" t="s">
@@ -10305,15 +10508,15 @@
       </c>
       <c r="S17" s="6">
         <f>COUNTBLANK(N1:N158)</f>
-        <v>3</v>
-      </c>
-      <c r="T17" s="1">
-        <f t="shared" si="1"/>
-        <v>17.700307017543864</v>
-      </c>
-      <c r="U17" s="1">
-        <f t="shared" si="0"/>
-        <v>13.79</v>
+        <v>0</v>
+      </c>
+      <c r="T17" s="12">
+        <f>AVERAGE(N1:N158)</f>
+        <v>23.847133757961782</v>
+      </c>
+      <c r="U17" s="8">
+        <f>MEDIAN(N2:N158)</f>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
@@ -10323,10 +10526,10 @@
       <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="7">
         <v>6.5359999999999996</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="7">
         <v>25.725000000000001</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -10362,7 +10565,7 @@
       <c r="O18" s="3">
         <v>40874</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="7">
         <v>113.7658739</v>
       </c>
       <c r="R18" s="10" t="s">
@@ -10372,13 +10575,11 @@
         <f>COUNTBLANK(O2:O158)</f>
         <v>0</v>
       </c>
-      <c r="T18" s="1">
-        <f t="shared" si="1"/>
-        <v>17.603185840707969</v>
-      </c>
-      <c r="U18" s="1">
-        <f t="shared" si="0"/>
-        <v>13.782499999999999</v>
+      <c r="T18" s="8">
+        <v>0</v>
+      </c>
+      <c r="U18" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
@@ -10388,10 +10589,10 @@
       <c r="B19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="7">
         <v>11.185</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="7">
         <v>18.225000000000001</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -10427,7 +10628,7 @@
       <c r="O19" s="3">
         <v>40814</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="7">
         <v>83.483093580000002</v>
       </c>
       <c r="R19" s="10" t="s">
@@ -10435,15 +10636,15 @@
       </c>
       <c r="S19" s="6">
         <f>COUNTBLANK(P2:P158)</f>
-        <v>2</v>
-      </c>
-      <c r="T19" s="1">
-        <f>AVERAGE(P12:P168)</f>
-        <v>76.586639233698619</v>
-      </c>
-      <c r="U19" s="1">
-        <f t="shared" si="0"/>
-        <v>13.79</v>
+        <v>0</v>
+      </c>
+      <c r="T19" s="12">
+        <f>AVERAGE(P1:P158)</f>
+        <v>76.979723796942679</v>
+      </c>
+      <c r="U19" s="12">
+        <f>MEDIAN(P2:P158)</f>
+        <v>72.03</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
@@ -10453,10 +10654,13 @@
       <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="7">
         <v>14.785</v>
       </c>
-      <c r="D20" s="5"/>
+      <c r="D20" s="11">
+        <f>Car_sales_Cleaned!D13</f>
+        <v>13.74</v>
+      </c>
       <c r="E20" s="1" t="s">
         <v>41</v>
       </c>
@@ -10490,7 +10694,7 @@
       <c r="O20" s="3">
         <v>41016</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="7">
         <v>109.5091165</v>
       </c>
     </row>
@@ -10501,10 +10705,10 @@
       <c r="B21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="7">
         <v>145.51900000000001</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="7">
         <v>9.25</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -10540,7 +10744,7 @@
       <c r="O21" s="3">
         <v>40772</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="7">
         <v>46.363347470000001</v>
       </c>
       <c r="R21" s="8"/>
@@ -10553,10 +10757,10 @@
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="7">
         <v>135.126</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="7">
         <v>11.225</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -10592,7 +10796,7 @@
       <c r="O22" s="3">
         <v>40987</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="7">
         <v>67.314462160000005</v>
       </c>
       <c r="S22" s="9"/>
@@ -10604,10 +10808,10 @@
       <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="7">
         <v>24.629000000000001</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="7">
         <v>10.31</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -10643,7 +10847,7 @@
       <c r="O23" s="3">
         <v>40687</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="7">
         <v>69.991395600000004</v>
       </c>
       <c r="S23" s="8"/>
@@ -10655,10 +10859,10 @@
       <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="7">
         <v>42.593000000000004</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="7">
         <v>11.525</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -10694,7 +10898,7 @@
       <c r="O24" s="3">
         <v>40899</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="7">
         <v>72.030917189999997</v>
       </c>
     </row>
@@ -10705,10 +10909,10 @@
       <c r="B25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="7">
         <v>26.402000000000001</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="7">
         <v>13.025</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -10744,7 +10948,7 @@
       <c r="O25" s="3">
         <v>40839</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="7">
         <v>81.118543329999994</v>
       </c>
     </row>
@@ -10755,10 +10959,10 @@
       <c r="B26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="7">
         <v>17.946999999999999</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="7">
         <v>36.225000000000001</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -10794,7 +10998,7 @@
       <c r="O26" s="3">
         <v>41041</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="7">
         <v>141.14115000000001</v>
       </c>
     </row>
@@ -10805,10 +11009,10 @@
       <c r="B27" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="7">
         <v>32.298999999999999</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="7">
         <v>9.125</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -10844,7 +11048,7 @@
       <c r="O27" s="3">
         <v>40797</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="7">
         <v>48.297636099999998</v>
       </c>
     </row>
@@ -10855,10 +11059,10 @@
       <c r="B28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="7">
         <v>21.855</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="7">
         <v>5.16</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -10894,7 +11098,7 @@
       <c r="O28" s="3">
         <v>41012</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="7">
         <v>23.276272330000001</v>
       </c>
     </row>
@@ -10905,10 +11109,13 @@
       <c r="B29" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="7">
         <v>107.995</v>
       </c>
-      <c r="D29" s="5"/>
+      <c r="D29" s="11">
+        <f>Car_sales_Cleaned!D22</f>
+        <v>11.225</v>
+      </c>
       <c r="E29" s="1" t="s">
         <v>18</v>
       </c>
@@ -10942,7 +11149,7 @@
       <c r="O29" s="3">
         <v>40712</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="7">
         <v>71.838039440000003</v>
       </c>
     </row>
@@ -10953,10 +11160,10 @@
       <c r="B30" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="7">
         <v>7.8540000000000001</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" s="7">
         <v>12.36</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -10992,7 +11199,7 @@
       <c r="O30" s="3">
         <v>40924</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="7">
         <v>65.957183959999995</v>
       </c>
     </row>
@@ -11003,10 +11210,10 @@
       <c r="B31" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="7">
         <v>32.774999999999999</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="7">
         <v>14.18</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -11042,7 +11249,7 @@
       <c r="O31" s="3">
         <v>40864</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="7">
         <v>69.521355049999997</v>
       </c>
     </row>
@@ -11053,10 +11260,10 @@
       <c r="B32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="7">
         <v>31.148</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="7">
         <v>13.725</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -11092,7 +11299,7 @@
       <c r="O32" s="3">
         <v>41066</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="7">
         <v>80.02378204</v>
       </c>
     </row>
@@ -11103,10 +11310,10 @@
       <c r="B33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="7">
         <v>32.305999999999997</v>
       </c>
-      <c r="D33" s="1">
+      <c r="D33" s="7">
         <v>12.64</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -11142,7 +11349,7 @@
       <c r="O33" s="3">
         <v>40822</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="7">
         <v>53.566199869999998</v>
       </c>
     </row>
@@ -11153,10 +11360,10 @@
       <c r="B34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="7">
         <v>13.462</v>
       </c>
-      <c r="D34" s="1">
+      <c r="D34" s="7">
         <v>17.324999999999999</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -11192,7 +11399,7 @@
       <c r="O34" s="3">
         <v>41037</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="7">
         <v>101.3292807</v>
       </c>
     </row>
@@ -11203,28 +11410,58 @@
       <c r="B35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="7">
         <v>53.48</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="7">
         <v>19.54</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
+      <c r="F35" s="5">
+        <f>22.8</f>
+        <v>22.8</v>
+      </c>
+      <c r="G35" s="5">
+        <f>3</f>
+        <v>3</v>
+      </c>
+      <c r="H35" s="5">
+        <f>177.5</f>
+        <v>177.5</v>
+      </c>
+      <c r="I35" s="5">
+        <f>107</f>
+        <v>107</v>
+      </c>
+      <c r="J35" s="5">
+        <f>70.55</f>
+        <v>70.55</v>
+      </c>
+      <c r="K35" s="5">
+        <f>187.9</f>
+        <v>187.9</v>
+      </c>
+      <c r="L35" s="5">
+        <f>3.342</f>
+        <v>3.3420000000000001</v>
+      </c>
+      <c r="M35" s="5">
+        <f>17.2</f>
+        <v>17.2</v>
+      </c>
+      <c r="N35" s="5">
+        <f>24</f>
+        <v>24</v>
+      </c>
       <c r="O35" s="3">
         <v>40737</v>
       </c>
-      <c r="P35" s="5"/>
+      <c r="P35" s="11">
+        <f>72.03</f>
+        <v>72.03</v>
+      </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -11233,10 +11470,13 @@
       <c r="B36" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="7">
         <v>30.696000000000002</v>
       </c>
-      <c r="D36" s="5"/>
+      <c r="D36" s="11">
+        <f>Car_sales_Cleaned!D29</f>
+        <v>11.225</v>
+      </c>
       <c r="E36" s="1" t="s">
         <v>18</v>
       </c>
@@ -11270,7 +11510,7 @@
       <c r="O36" s="3">
         <v>40949</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="7">
         <v>101.6552441</v>
       </c>
     </row>
@@ -11281,10 +11521,10 @@
       <c r="B37" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="7">
         <v>76.034000000000006</v>
       </c>
-      <c r="D37" s="1">
+      <c r="D37" s="7">
         <v>7.75</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -11320,7 +11560,7 @@
       <c r="O37" s="3">
         <v>40889</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="7">
         <v>52.084898750000001</v>
       </c>
     </row>
@@ -11331,10 +11571,10 @@
       <c r="B38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="7">
         <v>4.734</v>
       </c>
-      <c r="D38" s="1">
+      <c r="D38" s="7">
         <v>12.545</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -11370,7 +11610,7 @@
       <c r="O38" s="3">
         <v>41091</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="7">
         <v>65.650508340000002</v>
       </c>
     </row>
@@ -11381,10 +11621,10 @@
       <c r="B39" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="7">
         <v>71.186000000000007</v>
       </c>
-      <c r="D39" s="1">
+      <c r="D39" s="7">
         <v>10.185</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -11420,7 +11660,7 @@
       <c r="O39" s="3">
         <v>40847</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="7">
         <v>67.876107840000003</v>
       </c>
     </row>
@@ -11431,10 +11671,10 @@
       <c r="B40" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="7">
         <v>88.028000000000006</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="7">
         <v>12.275</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -11464,11 +11704,14 @@
       <c r="M40" s="1">
         <v>17</v>
       </c>
-      <c r="N40" s="5"/>
+      <c r="N40" s="5">
+        <f>24</f>
+        <v>24</v>
+      </c>
       <c r="O40" s="3">
         <v>41062</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="7">
         <v>80.831470170000003</v>
       </c>
     </row>
@@ -11479,10 +11722,10 @@
       <c r="B41" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="7">
         <v>0.91600000000000004</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="7">
         <v>58.47</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -11518,7 +11761,7 @@
       <c r="O41" s="3">
         <v>40762</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P41" s="7">
         <v>188.14432300000001</v>
       </c>
     </row>
@@ -11529,10 +11772,10 @@
       <c r="B42" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="7">
         <v>227.06100000000001</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="7">
         <v>15.06</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -11568,7 +11811,7 @@
       <c r="O42" s="3">
         <v>40974</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P42" s="7">
         <v>90.211700050000005</v>
       </c>
     </row>
@@ -11579,10 +11822,10 @@
       <c r="B43" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="7">
         <v>16.766999999999999</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D43" s="7">
         <v>15.51</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -11618,7 +11861,7 @@
       <c r="O43" s="3">
         <v>40914</v>
       </c>
-      <c r="P43" s="1">
+      <c r="P43" s="7">
         <v>71.135291609999996</v>
       </c>
     </row>
@@ -11629,10 +11872,10 @@
       <c r="B44" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="7">
         <v>31.038</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="7">
         <v>13.425000000000001</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -11668,7 +11911,7 @@
       <c r="O44" s="3">
         <v>41116</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P44" s="7">
         <v>70.078321540000005</v>
       </c>
     </row>
@@ -11679,10 +11922,10 @@
       <c r="B45" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="7">
         <v>111.313</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="7">
         <v>11.26</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -11718,7 +11961,7 @@
       <c r="O45" s="3">
         <v>40872</v>
       </c>
-      <c r="P45" s="1">
+      <c r="P45" s="7">
         <v>49.64500177</v>
       </c>
     </row>
@@ -11729,10 +11972,13 @@
       <c r="B46" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="7">
         <v>101.32299999999999</v>
       </c>
-      <c r="D46" s="5"/>
+      <c r="D46" s="11">
+        <f>Car_sales_Cleaned!D39</f>
+        <v>10.185</v>
+      </c>
       <c r="E46" s="1" t="s">
         <v>41</v>
       </c>
@@ -11766,7 +12012,7 @@
       <c r="O46" s="3">
         <v>41087</v>
       </c>
-      <c r="P46" s="1">
+      <c r="P46" s="7">
         <v>92.85412522</v>
       </c>
     </row>
@@ -11777,10 +12023,10 @@
       <c r="B47" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="7">
         <v>181.749</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="7">
         <v>12.025</v>
       </c>
       <c r="E47" s="1" t="s">
@@ -11816,7 +12062,7 @@
       <c r="O47" s="3">
         <v>40787</v>
       </c>
-      <c r="P47" s="1">
+      <c r="P47" s="7">
         <v>61.227000310000001</v>
       </c>
     </row>
@@ -11827,10 +12073,10 @@
       <c r="B48" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="7">
         <v>70.227000000000004</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D48" s="7">
         <v>7.4249999999999998</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -11866,7 +12112,7 @@
       <c r="O48" s="3">
         <v>40999</v>
       </c>
-      <c r="P48" s="1">
+      <c r="P48" s="7">
         <v>44.083709460000001</v>
       </c>
     </row>
@@ -11877,10 +12123,10 @@
       <c r="B49" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="7">
         <v>113.369</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="7">
         <v>12.76</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -11916,7 +12162,7 @@
       <c r="O49" s="3">
         <v>40939</v>
       </c>
-      <c r="P49" s="1">
+      <c r="P49" s="7">
         <v>76.509184559999994</v>
       </c>
     </row>
@@ -11927,10 +12173,10 @@
       <c r="B50" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="7">
         <v>35.067999999999998</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="7">
         <v>8.8350000000000009</v>
       </c>
       <c r="E50" s="1" t="s">
@@ -11966,7 +12212,7 @@
       <c r="O50" s="3">
         <v>41141</v>
       </c>
-      <c r="P50" s="1">
+      <c r="P50" s="7">
         <v>67.351010720000005</v>
       </c>
     </row>
@@ -11977,10 +12223,10 @@
       <c r="B51" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="7">
         <v>245.815</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" s="7">
         <v>10.055</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -12016,7 +12262,7 @@
       <c r="O51" s="3">
         <v>40897</v>
       </c>
-      <c r="P51" s="1">
+      <c r="P51" s="7">
         <v>62.503739500000002</v>
       </c>
     </row>
@@ -12027,10 +12273,13 @@
       <c r="B52" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="7">
         <v>175.67</v>
       </c>
-      <c r="D52" s="5"/>
+      <c r="D52" s="11">
+        <f>Car_sales_Cleaned!D45</f>
+        <v>11.26</v>
+      </c>
       <c r="E52" s="1" t="s">
         <v>18</v>
       </c>
@@ -12064,7 +12313,7 @@
       <c r="O52" s="3">
         <v>41112</v>
       </c>
-      <c r="P52" s="1">
+      <c r="P52" s="7">
         <v>43.117132009999999</v>
       </c>
     </row>
@@ -12075,10 +12324,10 @@
       <c r="B53" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="7">
         <v>63.402999999999999</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="7">
         <v>14.21</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -12114,7 +12363,7 @@
       <c r="O53" s="3">
         <v>40812</v>
       </c>
-      <c r="P53" s="1">
+      <c r="P53" s="7">
         <v>80.499536710000001</v>
       </c>
     </row>
@@ -12125,10 +12374,10 @@
       <c r="B54" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="7">
         <v>276.74700000000001</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D54" s="7">
         <v>16.64</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -12164,7 +12413,7 @@
       <c r="O54" s="3">
         <v>41024</v>
       </c>
-      <c r="P54" s="1">
+      <c r="P54" s="7">
         <v>87.635495779999999</v>
       </c>
     </row>
@@ -12175,10 +12424,10 @@
       <c r="B55" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="7">
         <v>155.78700000000001</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="7">
         <v>13.175000000000001</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -12214,7 +12463,7 @@
       <c r="O55" s="3">
         <v>40964</v>
       </c>
-      <c r="P55" s="1">
+      <c r="P55" s="7">
         <v>62.095048390000002</v>
       </c>
     </row>
@@ -12225,10 +12474,10 @@
       <c r="B56" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="7">
         <v>125.33799999999999</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="7">
         <v>23.574999999999999</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -12264,7 +12513,7 @@
       <c r="O56" s="3">
         <v>41166</v>
       </c>
-      <c r="P56" s="1">
+      <c r="P56" s="7">
         <v>100.0248023</v>
       </c>
     </row>
@@ -12275,10 +12524,10 @@
       <c r="B57" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57" s="7">
         <v>220.65</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="7">
         <v>7.85</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -12314,7 +12563,7 @@
       <c r="O57" s="3">
         <v>40922</v>
       </c>
-      <c r="P57" s="1">
+      <c r="P57" s="7">
         <v>47.389531310000002</v>
       </c>
     </row>
@@ -12325,10 +12574,10 @@
       <c r="B58" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58" s="7">
         <v>540.56100000000004</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D58" s="7">
         <v>15.074999999999999</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -12364,7 +12613,7 @@
       <c r="O58" s="3">
         <v>41137</v>
       </c>
-      <c r="P58" s="1">
+      <c r="P58" s="7">
         <v>89.401934729999994</v>
       </c>
     </row>
@@ -12375,10 +12624,10 @@
       <c r="B59" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59" s="7">
         <v>199.685</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="7">
         <v>9.85</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -12414,7 +12663,7 @@
       <c r="O59" s="3">
         <v>40837</v>
       </c>
-      <c r="P59" s="1">
+      <c r="P59" s="7">
         <v>42.879097340000001</v>
       </c>
     </row>
@@ -12425,10 +12674,10 @@
       <c r="B60" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60" s="7">
         <v>230.90199999999999</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D60" s="7">
         <v>13.21</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -12464,7 +12713,7 @@
       <c r="O60" s="3">
         <v>41049</v>
       </c>
-      <c r="P60" s="1">
+      <c r="P60" s="7">
         <v>54.269548290000003</v>
       </c>
     </row>
@@ -12475,10 +12724,10 @@
       <c r="B61" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61" s="7">
         <v>73.203000000000003</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D61" s="7">
         <v>17.71</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -12514,7 +12763,7 @@
       <c r="O61" s="3">
         <v>40989</v>
       </c>
-      <c r="P61" s="1">
+      <c r="P61" s="7">
         <v>60.087966620000003</v>
       </c>
     </row>
@@ -12525,10 +12774,10 @@
       <c r="B62" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C62" s="7">
         <v>12.855</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D62" s="7">
         <v>17.524999999999999</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -12564,7 +12813,7 @@
       <c r="O62" s="3">
         <v>41191</v>
       </c>
-      <c r="P62" s="1">
+      <c r="P62" s="7">
         <v>83.602500800000001</v>
       </c>
     </row>
@@ -12575,10 +12824,10 @@
       <c r="B63" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="7">
         <v>76.028999999999996</v>
       </c>
-      <c r="D63" s="1">
+      <c r="D63" s="7">
         <v>19.489999999999998</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -12614,7 +12863,7 @@
       <c r="O63" s="3">
         <v>40947</v>
       </c>
-      <c r="P63" s="1">
+      <c r="P63" s="7">
         <v>85.217691340000002</v>
       </c>
     </row>
@@ -12625,10 +12874,10 @@
       <c r="B64" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="7">
         <v>41.183999999999997</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" s="7">
         <v>5.86</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -12664,7 +12913,7 @@
       <c r="O64" s="3">
         <v>41162</v>
       </c>
-      <c r="P64" s="1">
+      <c r="P64" s="7">
         <v>36.672283579999998</v>
       </c>
     </row>
@@ -12675,10 +12924,10 @@
       <c r="B65" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="7">
         <v>66.691999999999993</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="7">
         <v>7.8250000000000002</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -12714,7 +12963,7 @@
       <c r="O65" s="3">
         <v>40862</v>
       </c>
-      <c r="P65" s="1">
+      <c r="P65" s="7">
         <v>54.590045160000003</v>
       </c>
     </row>
@@ -12725,10 +12974,10 @@
       <c r="B66" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="7">
         <v>29.45</v>
       </c>
-      <c r="D66" s="1">
+      <c r="D66" s="7">
         <v>8.91</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -12764,7 +13013,7 @@
       <c r="O66" s="3">
         <v>41074</v>
       </c>
-      <c r="P66" s="1">
+      <c r="P66" s="7">
         <v>58.758248999999999</v>
       </c>
     </row>
@@ -12775,10 +13024,10 @@
       <c r="B67" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="7">
         <v>23.713000000000001</v>
       </c>
-      <c r="D67" s="1">
+      <c r="D67" s="7">
         <v>19.690000000000001</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -12814,7 +13063,7 @@
       <c r="O67" s="3">
         <v>41014</v>
       </c>
-      <c r="P67" s="1">
+      <c r="P67" s="7">
         <v>92.436889230000006</v>
       </c>
     </row>
@@ -12825,10 +13074,13 @@
       <c r="B68" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="7">
         <v>15.467000000000001</v>
       </c>
-      <c r="D68" s="5"/>
+      <c r="D68" s="11">
+        <f>Car_sales_Cleaned!D61</f>
+        <v>17.71</v>
+      </c>
       <c r="E68" s="1" t="s">
         <v>18</v>
       </c>
@@ -12862,7 +13114,7 @@
       <c r="O68" s="3">
         <v>41216</v>
       </c>
-      <c r="P68" s="1">
+      <c r="P68" s="7">
         <v>102.17898479999999</v>
       </c>
     </row>
@@ -12873,10 +13125,10 @@
       <c r="B69" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69" s="7">
         <v>55.557000000000002</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D69" s="7">
         <v>13.475</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -12912,7 +13164,7 @@
       <c r="O69" s="3">
         <v>40972</v>
       </c>
-      <c r="P69" s="1">
+      <c r="P69" s="7">
         <v>48.672897910000003</v>
       </c>
     </row>
@@ -12923,10 +13175,10 @@
       <c r="B70" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="7">
         <v>80.555999999999997</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70" s="7">
         <v>13.775</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -12962,7 +13214,7 @@
       <c r="O70" s="3">
         <v>41187</v>
       </c>
-      <c r="P70" s="1">
+      <c r="P70" s="7">
         <v>76.584439619999998</v>
       </c>
     </row>
@@ -12973,10 +13225,10 @@
       <c r="B71" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71" s="7">
         <v>157.04</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71" s="7">
         <v>18.809999999999999</v>
       </c>
       <c r="E71" s="1" t="s">
@@ -13012,7 +13264,7 @@
       <c r="O71" s="3">
         <v>40887</v>
       </c>
-      <c r="P71" s="1">
+      <c r="P71" s="7">
         <v>80.387779120000005</v>
       </c>
     </row>
@@ -13023,10 +13275,10 @@
       <c r="B72" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="7">
         <v>24.071999999999999</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72" s="7">
         <v>26.975000000000001</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -13062,7 +13314,7 @@
       <c r="O72" s="3">
         <v>41099</v>
       </c>
-      <c r="P72" s="1">
+      <c r="P72" s="7">
         <v>87.211001039999999</v>
       </c>
     </row>
@@ -13073,10 +13325,10 @@
       <c r="B73" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C73" s="7">
         <v>12.698</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D73" s="7">
         <v>32.075000000000003</v>
       </c>
       <c r="E73" s="1" t="s">
@@ -13112,7 +13364,7 @@
       <c r="O73" s="3">
         <v>41039</v>
       </c>
-      <c r="P73" s="1">
+      <c r="P73" s="7">
         <v>94.946698400000002</v>
       </c>
     </row>
@@ -13123,10 +13375,13 @@
       <c r="B74" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74" s="7">
         <v>3.3340000000000001</v>
       </c>
-      <c r="D74" s="5"/>
+      <c r="D74" s="11">
+        <f>Car_sales_Cleaned!D67</f>
+        <v>19.690000000000001</v>
+      </c>
       <c r="E74" s="1" t="s">
         <v>18</v>
       </c>
@@ -13160,7 +13415,7 @@
       <c r="O74" s="3">
         <v>41241</v>
       </c>
-      <c r="P74" s="1">
+      <c r="P74" s="7">
         <v>125.0133574</v>
       </c>
     </row>
@@ -13171,10 +13426,10 @@
       <c r="B75" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="7">
         <v>6.375</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="7">
         <v>40.375</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -13210,7 +13465,7 @@
       <c r="O75" s="3">
         <v>40997</v>
       </c>
-      <c r="P75" s="1">
+      <c r="P75" s="7">
         <v>124.44671630000001</v>
       </c>
     </row>
@@ -13221,10 +13476,13 @@
       <c r="B76" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="7">
         <v>9.1259999999999994</v>
       </c>
-      <c r="D76" s="5"/>
+      <c r="D76" s="11">
+        <f>Car_sales_Cleaned!D69</f>
+        <v>13.475</v>
+      </c>
       <c r="E76" s="1" t="s">
         <v>41</v>
       </c>
@@ -13258,7 +13516,7 @@
       <c r="O76" s="3">
         <v>41212</v>
       </c>
-      <c r="P76" s="1">
+      <c r="P76" s="7">
         <v>105.760458</v>
       </c>
     </row>
@@ -13269,10 +13527,13 @@
       <c r="B77" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C77" s="7">
         <v>51.238</v>
       </c>
-      <c r="D77" s="5"/>
+      <c r="D77" s="11">
+        <f>Car_sales_Cleaned!D70</f>
+        <v>13.775</v>
+      </c>
       <c r="E77" s="1" t="s">
         <v>41</v>
       </c>
@@ -13306,7 +13567,7 @@
       <c r="O77" s="3">
         <v>40912</v>
       </c>
-      <c r="P77" s="1">
+      <c r="P77" s="7">
         <v>91.943801559999997</v>
       </c>
     </row>
@@ -13317,10 +13578,10 @@
       <c r="B78" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="7">
         <v>13.798</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D78" s="7">
         <v>20.524999999999999</v>
       </c>
       <c r="E78" s="1" t="s">
@@ -13356,7 +13617,7 @@
       <c r="O78" s="3">
         <v>41124</v>
       </c>
-      <c r="P78" s="1">
+      <c r="P78" s="7">
         <v>113.5402069</v>
       </c>
     </row>
@@ -13367,10 +13628,10 @@
       <c r="B79" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C79" s="1">
+      <c r="C79" s="7">
         <v>48.911000000000001</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D79" s="7">
         <v>21.725000000000001</v>
       </c>
       <c r="E79" s="1" t="s">
@@ -13406,7 +13667,7 @@
       <c r="O79" s="3">
         <v>41064</v>
       </c>
-      <c r="P79" s="1">
+      <c r="P79" s="7">
         <v>93.957916900000001</v>
       </c>
     </row>
@@ -13417,10 +13678,13 @@
       <c r="B80" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C80" s="1">
+      <c r="C80" s="7">
         <v>22.925000000000001</v>
       </c>
-      <c r="D80" s="5"/>
+      <c r="D80" s="11">
+        <f>Car_sales_Cleaned!D73</f>
+        <v>32.075000000000003</v>
+      </c>
       <c r="E80" s="1" t="s">
         <v>41</v>
       </c>
@@ -13454,7 +13718,7 @@
       <c r="O80" s="3">
         <v>41266</v>
       </c>
-      <c r="P80" s="1">
+      <c r="P80" s="7">
         <v>123.97204670000001</v>
       </c>
     </row>
@@ -13465,10 +13729,10 @@
       <c r="B81" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C81" s="1">
+      <c r="C81" s="7">
         <v>26.231999999999999</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D81" s="7">
         <v>8.3249999999999993</v>
       </c>
       <c r="E81" s="1" t="s">
@@ -13504,7 +13768,7 @@
       <c r="O81" s="3">
         <v>41022</v>
       </c>
-      <c r="P81" s="1">
+      <c r="P81" s="7">
         <v>45.832180559999998</v>
       </c>
     </row>
@@ -13515,10 +13779,10 @@
       <c r="B82" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C82" s="7">
         <v>42.540999999999997</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D82" s="7">
         <v>10.395</v>
       </c>
       <c r="E82" s="1" t="s">
@@ -13554,7 +13818,7 @@
       <c r="O82" s="3">
         <v>41237</v>
       </c>
-      <c r="P82" s="1">
+      <c r="P82" s="7">
         <v>62.441962349999997</v>
       </c>
     </row>
@@ -13565,10 +13829,10 @@
       <c r="B83" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C83" s="1">
+      <c r="C83" s="7">
         <v>55.616</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D83" s="7">
         <v>10.595000000000001</v>
       </c>
       <c r="E83" s="1" t="s">
@@ -13604,7 +13868,7 @@
       <c r="O83" s="3">
         <v>40937</v>
       </c>
-      <c r="P83" s="1">
+      <c r="P83" s="7">
         <v>58.606772919999997</v>
       </c>
     </row>
@@ -13615,10 +13879,10 @@
       <c r="B84" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C84" s="7">
         <v>5.7110000000000003</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D84" s="7">
         <v>16.574999999999999</v>
       </c>
       <c r="E84" s="1" t="s">
@@ -13654,7 +13918,7 @@
       <c r="O84" s="3">
         <v>41149</v>
       </c>
-      <c r="P84" s="1">
+      <c r="P84" s="7">
         <v>84.83077858</v>
       </c>
     </row>
@@ -13665,10 +13929,10 @@
       <c r="B85" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C85" s="1">
+      <c r="C85" s="7">
         <v>0.11</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D85" s="7">
         <v>20.94</v>
       </c>
       <c r="E85" s="1" t="s">
@@ -13704,7 +13968,7 @@
       <c r="O85" s="3">
         <v>41089</v>
       </c>
-      <c r="P85" s="1">
+      <c r="P85" s="7">
         <v>67.544154939999999</v>
       </c>
     </row>
@@ -13715,10 +13979,10 @@
       <c r="B86" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C86" s="1">
+      <c r="C86" s="7">
         <v>11.337</v>
       </c>
-      <c r="D86" s="1">
+      <c r="D86" s="7">
         <v>19.125</v>
       </c>
       <c r="E86" s="1" t="s">
@@ -13754,7 +14018,7 @@
       <c r="O86" s="3">
         <v>40925</v>
       </c>
-      <c r="P86" s="1">
+      <c r="P86" s="7">
         <v>83.920815039999994</v>
       </c>
     </row>
@@ -13765,10 +14029,10 @@
       <c r="B87" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C87" s="1">
+      <c r="C87" s="7">
         <v>39.347999999999999</v>
       </c>
-      <c r="D87" s="1">
+      <c r="D87" s="7">
         <v>13.88</v>
       </c>
       <c r="E87" s="1" t="s">
@@ -13804,7 +14068,7 @@
       <c r="O87" s="3">
         <v>41047</v>
       </c>
-      <c r="P87" s="1">
+      <c r="P87" s="7">
         <v>70.660941789999995</v>
       </c>
     </row>
@@ -13815,10 +14079,10 @@
       <c r="B88" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C88" s="7">
         <v>14.351000000000001</v>
       </c>
-      <c r="D88" s="1">
+      <c r="D88" s="7">
         <v>8.8000000000000007</v>
       </c>
       <c r="E88" s="1" t="s">
@@ -13854,7 +14118,7 @@
       <c r="O88" s="3">
         <v>41262</v>
       </c>
-      <c r="P88" s="1">
+      <c r="P88" s="7">
         <v>50.997747609999998</v>
       </c>
     </row>
@@ -13865,10 +14129,10 @@
       <c r="B89" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C89" s="7">
         <v>26.529</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D89" s="7">
         <v>13.89</v>
       </c>
       <c r="E89" s="1" t="s">
@@ -13904,7 +14168,7 @@
       <c r="O89" s="3">
         <v>40962</v>
       </c>
-      <c r="P89" s="1">
+      <c r="P89" s="7">
         <v>51.113474259999997</v>
       </c>
     </row>
@@ -13915,10 +14179,10 @@
       <c r="B90" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C90" s="1">
+      <c r="C90" s="7">
         <v>67.956000000000003</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D90" s="7">
         <v>11.03</v>
       </c>
       <c r="E90" s="1" t="s">
@@ -13954,7 +14218,7 @@
       <c r="O90" s="3">
         <v>41174</v>
       </c>
-      <c r="P90" s="1">
+      <c r="P90" s="7">
         <v>62.239966629999998</v>
       </c>
     </row>
@@ -13965,10 +14229,10 @@
       <c r="B91" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C91" s="1">
+      <c r="C91" s="7">
         <v>81.174000000000007</v>
       </c>
-      <c r="D91" s="1">
+      <c r="D91" s="7">
         <v>14.875</v>
       </c>
       <c r="E91" s="1" t="s">
@@ -14004,7 +14268,7 @@
       <c r="O91" s="3">
         <v>41114</v>
       </c>
-      <c r="P91" s="1">
+      <c r="P91" s="7">
         <v>80.657696459999997</v>
       </c>
     </row>
@@ -14015,10 +14279,10 @@
       <c r="B92" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C92" s="1">
+      <c r="C92" s="7">
         <v>27.609000000000002</v>
       </c>
-      <c r="D92" s="1">
+      <c r="D92" s="7">
         <v>20.43</v>
       </c>
       <c r="E92" s="1" t="s">
@@ -14054,7 +14318,7 @@
       <c r="O92" s="3">
         <v>39491</v>
       </c>
-      <c r="P92" s="1">
+      <c r="P92" s="7">
         <v>85.949744249999995</v>
       </c>
     </row>
@@ -14065,10 +14329,10 @@
       <c r="B93" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C93" s="1">
+      <c r="C93" s="7">
         <v>20.38</v>
       </c>
-      <c r="D93" s="1">
+      <c r="D93" s="7">
         <v>14.795</v>
       </c>
       <c r="E93" s="1" t="s">
@@ -14104,7 +14368,7 @@
       <c r="O93" s="3">
         <v>40106</v>
       </c>
-      <c r="P93" s="1">
+      <c r="P93" s="7">
         <v>69.671460999999994</v>
       </c>
     </row>
@@ -14115,10 +14379,10 @@
       <c r="B94" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C94" s="1">
+      <c r="C94" s="7">
         <v>18.391999999999999</v>
       </c>
-      <c r="D94" s="1">
+      <c r="D94" s="7">
         <v>26.05</v>
       </c>
       <c r="E94" s="1" t="s">
@@ -14154,7 +14418,7 @@
       <c r="O94" s="3">
         <v>40657</v>
       </c>
-      <c r="P94" s="1">
+      <c r="P94" s="7">
         <v>78.280730879999993</v>
       </c>
     </row>
@@ -14165,10 +14429,10 @@
       <c r="B95" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C95" s="1">
+      <c r="C95" s="7">
         <v>27.602</v>
       </c>
-      <c r="D95" s="1">
+      <c r="D95" s="7">
         <v>41.45</v>
       </c>
       <c r="E95" s="1" t="s">
@@ -14204,7 +14468,7 @@
       <c r="O95" s="3">
         <v>40736</v>
       </c>
-      <c r="P95" s="1">
+      <c r="P95" s="7">
         <v>98.249737499999995</v>
       </c>
     </row>
@@ -14215,10 +14479,10 @@
       <c r="B96" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C96" s="1">
+      <c r="C96" s="7">
         <v>16.774000000000001</v>
       </c>
-      <c r="D96" s="1">
+      <c r="D96" s="7">
         <v>50.375</v>
       </c>
       <c r="E96" s="1" t="s">
@@ -14254,7 +14518,7 @@
       <c r="O96" s="3">
         <v>40707</v>
       </c>
-      <c r="P96" s="1">
+      <c r="P96" s="7">
         <v>125.2738757</v>
       </c>
     </row>
@@ -14265,10 +14529,10 @@
       <c r="B97" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C97" s="1">
+      <c r="C97" s="7">
         <v>3.3109999999999999</v>
       </c>
-      <c r="D97" s="1">
+      <c r="D97" s="7">
         <v>58.6</v>
       </c>
       <c r="E97" s="1" t="s">
@@ -14304,7 +14568,7 @@
       <c r="O97" s="3">
         <v>40619</v>
       </c>
-      <c r="P97" s="1">
+      <c r="P97" s="7">
         <v>139.98229359999999</v>
       </c>
     </row>
@@ -14315,10 +14579,13 @@
       <c r="B98" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C98" s="7">
         <v>7.9980000000000002</v>
       </c>
-      <c r="D98" s="5"/>
+      <c r="D98" s="11">
+        <f>Car_sales_Cleaned!D91</f>
+        <v>14.875</v>
+      </c>
       <c r="E98" s="1" t="s">
         <v>18</v>
       </c>
@@ -14352,7 +14619,7 @@
       <c r="O98" s="3">
         <v>40559</v>
       </c>
-      <c r="P98" s="1">
+      <c r="P98" s="7">
         <v>82.807361929999999</v>
       </c>
     </row>
@@ -14363,10 +14630,13 @@
       <c r="B99" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C99" s="1">
+      <c r="C99" s="7">
         <v>1.526</v>
       </c>
-      <c r="D99" s="5"/>
+      <c r="D99" s="11">
+        <f>Car_sales_Cleaned!D92</f>
+        <v>20.43</v>
+      </c>
       <c r="E99" s="1" t="s">
         <v>18</v>
       </c>
@@ -14400,7 +14670,7 @@
       <c r="O99" s="3">
         <v>40761</v>
       </c>
-      <c r="P99" s="1">
+      <c r="P99" s="7">
         <v>81.848969240000002</v>
       </c>
     </row>
@@ -14411,10 +14681,13 @@
       <c r="B100" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C100" s="1">
+      <c r="C100" s="7">
         <v>11.592000000000001</v>
       </c>
-      <c r="D100" s="5"/>
+      <c r="D100" s="11">
+        <f>Car_sales_Cleaned!D93</f>
+        <v>14.795</v>
+      </c>
       <c r="E100" s="1" t="s">
         <v>18</v>
       </c>
@@ -14448,7 +14721,7 @@
       <c r="O100" s="3">
         <v>40732</v>
       </c>
-      <c r="P100" s="1">
+      <c r="P100" s="7">
         <v>92.925791770000004</v>
       </c>
     </row>
@@ -14459,10 +14732,13 @@
       <c r="B101" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C101" s="1">
+      <c r="C101" s="7">
         <v>0.95399999999999996</v>
       </c>
-      <c r="D101" s="5"/>
+      <c r="D101" s="11">
+        <f>Car_sales_Cleaned!D94</f>
+        <v>26.05</v>
+      </c>
       <c r="E101" s="1" t="s">
         <v>18</v>
       </c>
@@ -14496,7 +14772,7 @@
       <c r="O101" s="3">
         <v>40644</v>
       </c>
-      <c r="P101" s="1">
+      <c r="P101" s="7">
         <v>141.10098450000001</v>
       </c>
     </row>
@@ -14507,10 +14783,13 @@
       <c r="B102" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C102" s="1">
+      <c r="C102" s="7">
         <v>28.975999999999999</v>
       </c>
-      <c r="D102" s="5"/>
+      <c r="D102" s="11">
+        <f>Car_sales_Cleaned!D95</f>
+        <v>41.45</v>
+      </c>
       <c r="E102" s="1" t="s">
         <v>41</v>
       </c>
@@ -14544,7 +14823,7 @@
       <c r="O102" s="3">
         <v>40584</v>
       </c>
-      <c r="P102" s="1">
+      <c r="P102" s="7">
         <v>90.495532130000001</v>
       </c>
     </row>
@@ -14555,10 +14834,10 @@
       <c r="B103" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C103" s="1">
+      <c r="C103" s="7">
         <v>42.643000000000001</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D103" s="7">
         <v>8.4499999999999993</v>
       </c>
       <c r="E103" s="1" t="s">
@@ -14594,7 +14873,7 @@
       <c r="O103" s="3">
         <v>40786</v>
       </c>
-      <c r="P103" s="1">
+      <c r="P103" s="7">
         <v>50.241977910000003</v>
       </c>
     </row>
@@ -14605,10 +14884,10 @@
       <c r="B104" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C104" s="1">
+      <c r="C104" s="7">
         <v>88.093999999999994</v>
       </c>
-      <c r="D104" s="1">
+      <c r="D104" s="7">
         <v>11.295</v>
       </c>
       <c r="E104" s="1" t="s">
@@ -14644,7 +14923,7 @@
       <c r="O104" s="3">
         <v>40757</v>
       </c>
-      <c r="P104" s="1">
+      <c r="P104" s="7">
         <v>63.313727829999998</v>
       </c>
     </row>
@@ -14655,10 +14934,10 @@
       <c r="B105" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C105" s="1">
+      <c r="C105" s="7">
         <v>79.852999999999994</v>
       </c>
-      <c r="D105" s="1">
+      <c r="D105" s="7">
         <v>15.125</v>
       </c>
       <c r="E105" s="1" t="s">
@@ -14694,7 +14973,7 @@
       <c r="O105" s="3">
         <v>40669</v>
       </c>
-      <c r="P105" s="1">
+      <c r="P105" s="7">
         <v>89.427820310000001</v>
       </c>
     </row>
@@ -14705,10 +14984,10 @@
       <c r="B106" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C106" s="1">
+      <c r="C106" s="7">
         <v>27.308</v>
       </c>
-      <c r="D106" s="1">
+      <c r="D106" s="7">
         <v>15.38</v>
       </c>
       <c r="E106" s="1" t="s">
@@ -14744,7 +15023,7 @@
       <c r="O106" s="3">
         <v>40609</v>
       </c>
-      <c r="P106" s="1">
+      <c r="P106" s="7">
         <v>71.171664129999996</v>
       </c>
     </row>
@@ -14755,10 +15034,10 @@
       <c r="B107" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C107" s="1">
+      <c r="C107" s="7">
         <v>42.573999999999998</v>
       </c>
-      <c r="D107" s="1">
+      <c r="D107" s="7">
         <v>17.809999999999999</v>
       </c>
       <c r="E107" s="1" t="s">
@@ -14794,7 +15073,7 @@
       <c r="O107" s="3">
         <v>40811</v>
       </c>
-      <c r="P107" s="1">
+      <c r="P107" s="7">
         <v>72.290355079999998</v>
       </c>
     </row>
@@ -14805,10 +15084,13 @@
       <c r="B108" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C108" s="1">
+      <c r="C108" s="7">
         <v>54.158000000000001</v>
       </c>
-      <c r="D108" s="5"/>
+      <c r="D108" s="11">
+        <f>Car_sales_Cleaned!D101</f>
+        <v>26.05</v>
+      </c>
       <c r="E108" s="1" t="s">
         <v>41</v>
       </c>
@@ -14842,7 +15124,7 @@
       <c r="O108" s="3">
         <v>40567</v>
       </c>
-      <c r="P108" s="1">
+      <c r="P108" s="7">
         <v>69.78294434</v>
       </c>
     </row>
@@ -14853,10 +15135,13 @@
       <c r="B109" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C109" s="1">
+      <c r="C109" s="7">
         <v>65.004999999999995</v>
       </c>
-      <c r="D109" s="5"/>
+      <c r="D109" s="11">
+        <f>Car_sales_Cleaned!D102</f>
+        <v>41.45</v>
+      </c>
       <c r="E109" s="1" t="s">
         <v>41</v>
       </c>
@@ -14890,7 +15175,7 @@
       <c r="O109" s="3">
         <v>40782</v>
       </c>
-      <c r="P109" s="1">
+      <c r="P109" s="7">
         <v>67.889270589999995</v>
       </c>
     </row>
@@ -14901,10 +15186,10 @@
       <c r="B110" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C110" s="1">
+      <c r="C110" s="7">
         <v>1.1120000000000001</v>
       </c>
-      <c r="D110" s="1">
+      <c r="D110" s="7">
         <v>11.24</v>
       </c>
       <c r="E110" s="1" t="s">
@@ -14940,7 +15225,7 @@
       <c r="O110" s="3">
         <v>40694</v>
       </c>
-      <c r="P110" s="1">
+      <c r="P110" s="7">
         <v>60.861611549999999</v>
       </c>
     </row>
@@ -14951,10 +15236,13 @@
       <c r="B111" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C111" s="1">
+      <c r="C111" s="7">
         <v>38.554000000000002</v>
       </c>
-      <c r="D111" s="5"/>
+      <c r="D111" s="11">
+        <f>Car_sales_Cleaned!D104</f>
+        <v>11.295</v>
+      </c>
       <c r="E111" s="1" t="s">
         <v>18</v>
       </c>
@@ -14982,11 +15270,14 @@
       <c r="M111" s="1">
         <v>18</v>
       </c>
-      <c r="N111" s="5"/>
+      <c r="N111" s="5">
+        <f>24</f>
+        <v>24</v>
+      </c>
       <c r="O111" s="3">
         <v>40634</v>
       </c>
-      <c r="P111" s="1">
+      <c r="P111" s="7">
         <v>86.272522910000006</v>
       </c>
     </row>
@@ -14997,10 +15288,13 @@
       <c r="B112" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C112" s="1">
+      <c r="C112" s="7">
         <v>80.254999999999995</v>
       </c>
-      <c r="D112" s="5"/>
+      <c r="D112" s="11">
+        <f>Car_sales_Cleaned!D105</f>
+        <v>15.125</v>
+      </c>
       <c r="E112" s="1" t="s">
         <v>18</v>
       </c>
@@ -15034,7 +15328,7 @@
       <c r="O112" s="3">
         <v>40106</v>
       </c>
-      <c r="P112" s="1">
+      <c r="P112" s="7">
         <v>60.727446929999999</v>
       </c>
     </row>
@@ -15045,10 +15339,10 @@
       <c r="B113" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C113" s="1">
+      <c r="C113" s="7">
         <v>14.69</v>
       </c>
-      <c r="D113" s="1">
+      <c r="D113" s="7">
         <v>19.89</v>
       </c>
       <c r="E113" s="1" t="s">
@@ -15084,7 +15378,7 @@
       <c r="O113" s="3">
         <v>40592</v>
       </c>
-      <c r="P113" s="1">
+      <c r="P113" s="7">
         <v>103.4416926</v>
       </c>
     </row>
@@ -15095,10 +15389,10 @@
       <c r="B114" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C114" s="1">
+      <c r="C114" s="7">
         <v>20.016999999999999</v>
       </c>
-      <c r="D114" s="1">
+      <c r="D114" s="7">
         <v>19.925000000000001</v>
       </c>
       <c r="E114" s="1" t="s">
@@ -15134,7 +15428,7 @@
       <c r="O114" s="3">
         <v>40807</v>
       </c>
-      <c r="P114" s="1">
+      <c r="P114" s="7">
         <v>80.511672590000003</v>
       </c>
     </row>
@@ -15145,10 +15439,10 @@
       <c r="B115" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C115" s="7">
         <v>24.361000000000001</v>
       </c>
-      <c r="D115" s="1">
+      <c r="D115" s="7">
         <v>15.24</v>
       </c>
       <c r="E115" s="1" t="s">
@@ -15184,7 +15478,7 @@
       <c r="O115" s="3">
         <v>40719</v>
       </c>
-      <c r="P115" s="1">
+      <c r="P115" s="7">
         <v>76.096570420000006</v>
       </c>
     </row>
@@ -15195,10 +15489,10 @@
       <c r="B116" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C116" s="7">
         <v>32.734000000000002</v>
       </c>
-      <c r="D116" s="1">
+      <c r="D116" s="7">
         <v>7.75</v>
       </c>
       <c r="E116" s="1" t="s">
@@ -15234,7 +15528,7 @@
       <c r="O116" s="3">
         <v>40659</v>
       </c>
-      <c r="P116" s="1">
+      <c r="P116" s="7">
         <v>52.084898750000001</v>
       </c>
     </row>
@@ -15245,10 +15539,10 @@
       <c r="B117" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C117" s="1">
+      <c r="C117" s="7">
         <v>5.24</v>
       </c>
-      <c r="D117" s="1">
+      <c r="D117" s="7">
         <v>9.8000000000000007</v>
       </c>
       <c r="E117" s="1" t="s">
@@ -15284,7 +15578,7 @@
       <c r="O117" s="3">
         <v>40861</v>
       </c>
-      <c r="P117" s="1">
+      <c r="P117" s="7">
         <v>53.411897670000002</v>
       </c>
     </row>
@@ -15295,10 +15589,10 @@
       <c r="B118" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C118" s="1">
+      <c r="C118" s="7">
         <v>24.155000000000001</v>
       </c>
-      <c r="D118" s="1">
+      <c r="D118" s="7">
         <v>12.025</v>
       </c>
       <c r="E118" s="1" t="s">
@@ -15334,7 +15628,7 @@
       <c r="O118" s="3">
         <v>40657</v>
       </c>
-      <c r="P118" s="1">
+      <c r="P118" s="7">
         <v>60.951185119999998</v>
       </c>
     </row>
@@ -15345,10 +15639,13 @@
       <c r="B119" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C119" s="1">
+      <c r="C119" s="7">
         <v>1.8720000000000001</v>
       </c>
-      <c r="D119" s="5"/>
+      <c r="D119" s="11">
+        <f>Car_sales_Cleaned!D112</f>
+        <v>15.125</v>
+      </c>
       <c r="E119" s="1" t="s">
         <v>18</v>
       </c>
@@ -15382,7 +15679,7 @@
       <c r="O119" s="3">
         <v>41087</v>
       </c>
-      <c r="P119" s="1">
+      <c r="P119" s="7">
         <v>106.98445630000001</v>
       </c>
     </row>
@@ -15393,10 +15690,10 @@
       <c r="B120" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C120" s="1">
+      <c r="C120" s="7">
         <v>51.645000000000003</v>
       </c>
-      <c r="D120" s="1">
+      <c r="D120" s="7">
         <v>13.79</v>
       </c>
       <c r="E120" s="1" t="s">
@@ -15432,7 +15729,7 @@
       <c r="O120" s="3">
         <v>40933</v>
       </c>
-      <c r="P120" s="1">
+      <c r="P120" s="7">
         <v>62.015870300000003</v>
       </c>
     </row>
@@ -15443,10 +15740,10 @@
       <c r="B121" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C121" s="1">
+      <c r="C121" s="7">
         <v>131.09700000000001</v>
       </c>
-      <c r="D121" s="1">
+      <c r="D121" s="7">
         <v>10.29</v>
       </c>
       <c r="E121" s="1" t="s">
@@ -15482,7 +15779,7 @@
       <c r="O121" s="3">
         <v>41239</v>
       </c>
-      <c r="P121" s="1">
+      <c r="P121" s="7">
         <v>70.389737260000004</v>
       </c>
     </row>
@@ -15493,10 +15790,10 @@
       <c r="B122" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C122" s="1">
+      <c r="C122" s="7">
         <v>19.911000000000001</v>
       </c>
-      <c r="D122" s="1">
+      <c r="D122" s="7">
         <v>17.805</v>
       </c>
       <c r="E122" s="1" t="s">
@@ -15532,7 +15829,7 @@
       <c r="O122" s="3">
         <v>41076</v>
       </c>
-      <c r="P122" s="1">
+      <c r="P122" s="7">
         <v>81.492726160000004</v>
       </c>
     </row>
@@ -15543,10 +15840,10 @@
       <c r="B123" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C123" s="1">
+      <c r="C123" s="7">
         <v>92.364000000000004</v>
       </c>
-      <c r="D123" s="1">
+      <c r="D123" s="7">
         <v>14.01</v>
       </c>
       <c r="E123" s="1" t="s">
@@ -15582,7 +15879,7 @@
       <c r="O123" s="3">
         <v>41197</v>
       </c>
-      <c r="P123" s="1">
+      <c r="P123" s="7">
         <v>78.318168130000004</v>
       </c>
     </row>
@@ -15593,10 +15890,10 @@
       <c r="B124" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="C124" s="1">
+      <c r="C124" s="7">
         <v>35.945</v>
       </c>
-      <c r="D124" s="1">
+      <c r="D124" s="7">
         <v>13.225</v>
       </c>
       <c r="E124" s="1" t="s">
@@ -15632,7 +15929,7 @@
       <c r="O124" s="3">
         <v>40681</v>
       </c>
-      <c r="P124" s="1">
+      <c r="P124" s="7">
         <v>82.661355599999993</v>
       </c>
     </row>
@@ -15643,10 +15940,13 @@
       <c r="B125" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C125" s="1">
+      <c r="C125" s="7">
         <v>39.572000000000003</v>
       </c>
-      <c r="D125" s="5"/>
+      <c r="D125" s="11">
+        <f>Car_sales_Cleaned!D118</f>
+        <v>12.025</v>
+      </c>
       <c r="E125" s="1" t="s">
         <v>41</v>
       </c>
@@ -15680,7 +15980,7 @@
       <c r="O125" s="3">
         <v>41112</v>
       </c>
-      <c r="P125" s="1">
+      <c r="P125" s="7">
         <v>76.208439519999999</v>
       </c>
     </row>
@@ -15691,10 +15991,10 @@
       <c r="B126" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C126" s="1">
+      <c r="C126" s="7">
         <v>8.9819999999999993</v>
       </c>
-      <c r="D126" s="1">
+      <c r="D126" s="7">
         <v>41.25</v>
       </c>
       <c r="E126" s="1" t="s">
@@ -15730,7 +16030,7 @@
       <c r="O126" s="3">
         <v>40958</v>
       </c>
-      <c r="P126" s="1">
+      <c r="P126" s="7">
         <v>93.437330700000004</v>
       </c>
     </row>
@@ -15741,10 +16041,10 @@
       <c r="B127" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C127" s="1">
+      <c r="C127" s="7">
         <v>1.28</v>
       </c>
-      <c r="D127" s="1">
+      <c r="D127" s="7">
         <v>60.625</v>
       </c>
       <c r="E127" s="1" t="s">
@@ -15780,7 +16080,7 @@
       <c r="O127" s="3">
         <v>41264</v>
       </c>
-      <c r="P127" s="1">
+      <c r="P127" s="7">
         <v>134.3909754</v>
       </c>
     </row>
@@ -15791,10 +16091,10 @@
       <c r="B128" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C128" s="1">
+      <c r="C128" s="7">
         <v>1.8660000000000001</v>
       </c>
-      <c r="D128" s="1">
+      <c r="D128" s="7">
         <v>67.55</v>
       </c>
       <c r="E128" s="1" t="s">
@@ -15830,7 +16130,7 @@
       <c r="O128" s="3">
         <v>40735</v>
       </c>
-      <c r="P128" s="1">
+      <c r="P128" s="7">
         <v>135.91470960000001</v>
       </c>
     </row>
@@ -15841,10 +16141,13 @@
       <c r="B129" s="4">
         <v>46270</v>
       </c>
-      <c r="C129" s="1">
+      <c r="C129" s="7">
         <v>9.1910000000000007</v>
       </c>
-      <c r="D129" s="5"/>
+      <c r="D129" s="11">
+        <f>Car_sales_Cleaned!D122</f>
+        <v>17.805</v>
+      </c>
       <c r="E129" s="1" t="s">
         <v>18</v>
       </c>
@@ -15878,7 +16181,7 @@
       <c r="O129" s="3">
         <v>41222</v>
       </c>
-      <c r="P129" s="1">
+      <c r="P129" s="7">
         <v>73.503778190000006</v>
       </c>
     </row>
@@ -15889,10 +16192,13 @@
       <c r="B130" s="4">
         <v>46268</v>
       </c>
-      <c r="C130" s="1">
+      <c r="C130" s="7">
         <v>12.115</v>
       </c>
-      <c r="D130" s="5"/>
+      <c r="D130" s="11">
+        <f>Car_sales_Cleaned!D123</f>
+        <v>14.01</v>
+      </c>
       <c r="E130" s="1" t="s">
         <v>18</v>
       </c>
@@ -15926,7 +16232,7 @@
       <c r="O130" s="3">
         <v>40706</v>
       </c>
-      <c r="P130" s="1">
+      <c r="P130" s="7">
         <v>76.02304771</v>
       </c>
     </row>
@@ -15937,10 +16243,10 @@
       <c r="B131" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C131" s="1">
+      <c r="C131" s="7">
         <v>80.62</v>
       </c>
-      <c r="D131" s="1">
+      <c r="D131" s="7">
         <v>9.1999999999999993</v>
       </c>
       <c r="E131" s="1" t="s">
@@ -15976,7 +16282,7 @@
       <c r="O131" s="3">
         <v>41137</v>
       </c>
-      <c r="P131" s="1">
+      <c r="P131" s="7">
         <v>39.986424749999998</v>
       </c>
     </row>
@@ -15987,10 +16293,10 @@
       <c r="B132" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C132" s="1">
+      <c r="C132" s="7">
         <v>24.545999999999999</v>
       </c>
-      <c r="D132" s="1">
+      <c r="D132" s="7">
         <v>10.59</v>
       </c>
       <c r="E132" s="1" t="s">
@@ -16026,7 +16332,7 @@
       <c r="O132" s="3">
         <v>40618</v>
       </c>
-      <c r="P132" s="1">
+      <c r="P132" s="7">
         <v>40.700072419999998</v>
       </c>
     </row>
@@ -16037,10 +16343,10 @@
       <c r="B133" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C133" s="1">
+      <c r="C133" s="7">
         <v>5.2229999999999999</v>
       </c>
-      <c r="D133" s="1">
+      <c r="D133" s="7">
         <v>10.79</v>
       </c>
       <c r="E133" s="1" t="s">
@@ -16076,7 +16382,7 @@
       <c r="O133" s="3">
         <v>40558</v>
       </c>
-      <c r="P133" s="1">
+      <c r="P133" s="7">
         <v>49.865773670000003</v>
       </c>
     </row>
@@ -16087,10 +16393,13 @@
       <c r="B134" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C134" s="1">
+      <c r="C134" s="7">
         <v>8.4719999999999995</v>
       </c>
-      <c r="D134" s="5"/>
+      <c r="D134" s="11">
+        <f>Car_sales_Cleaned!D127</f>
+        <v>60.625</v>
+      </c>
       <c r="E134" s="1" t="s">
         <v>18</v>
       </c>
@@ -16124,7 +16433,7 @@
       <c r="O134" s="3">
         <v>40760</v>
       </c>
-      <c r="P134" s="1">
+      <c r="P134" s="7">
         <v>56.295243040000003</v>
       </c>
     </row>
@@ -16135,10 +16444,13 @@
       <c r="B135" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C135" s="1">
+      <c r="C135" s="7">
         <v>49.988999999999997</v>
       </c>
-      <c r="D135" s="5"/>
+      <c r="D135" s="11">
+        <f>Car_sales_Cleaned!D128</f>
+        <v>67.55</v>
+      </c>
       <c r="E135" s="1" t="s">
         <v>18</v>
       </c>
@@ -16172,7 +16484,7 @@
       <c r="O135" s="3">
         <v>41247</v>
       </c>
-      <c r="P135" s="1">
+      <c r="P135" s="7">
         <v>54.819728249999997</v>
       </c>
     </row>
@@ -16183,10 +16495,13 @@
       <c r="B136" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C136" s="1">
+      <c r="C136" s="7">
         <v>47.106999999999999</v>
       </c>
-      <c r="D136" s="5"/>
+      <c r="D136" s="11">
+        <f>Car_sales_Cleaned!D129</f>
+        <v>17.805</v>
+      </c>
       <c r="E136" s="1" t="s">
         <v>18</v>
       </c>
@@ -16220,7 +16535,7 @@
       <c r="O136" s="3">
         <v>40731</v>
       </c>
-      <c r="P136" s="1">
+      <c r="P136" s="7">
         <v>67.765907600000006</v>
       </c>
     </row>
@@ -16231,10 +16546,13 @@
       <c r="B137" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C137" s="1">
+      <c r="C137" s="7">
         <v>33.027999999999999</v>
       </c>
-      <c r="D137" s="5"/>
+      <c r="D137" s="11">
+        <f>Car_sales_Cleaned!D130</f>
+        <v>14.01</v>
+      </c>
       <c r="E137" s="1" t="s">
         <v>41</v>
       </c>
@@ -16268,7 +16586,7 @@
       <c r="O137" s="3">
         <v>41162</v>
       </c>
-      <c r="P137" s="1">
+      <c r="P137" s="7">
         <v>66.762943309999997</v>
       </c>
     </row>
@@ -16279,10 +16597,10 @@
       <c r="B138" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C138" s="1">
+      <c r="C138" s="7">
         <v>142.535</v>
       </c>
-      <c r="D138" s="1">
+      <c r="D138" s="7">
         <v>10.025</v>
       </c>
       <c r="E138" s="1" t="s">
@@ -16318,7 +16636,7 @@
       <c r="O138" s="3">
         <v>40644</v>
       </c>
-      <c r="P138" s="1">
+      <c r="P138" s="7">
         <v>47.96897242</v>
       </c>
     </row>
@@ -16329,10 +16647,10 @@
       <c r="B139" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C139" s="1">
+      <c r="C139" s="7">
         <v>247.994</v>
       </c>
-      <c r="D139" s="1">
+      <c r="D139" s="7">
         <v>13.244999999999999</v>
       </c>
       <c r="E139" s="1" t="s">
@@ -16368,7 +16686,7 @@
       <c r="O139" s="3">
         <v>40584</v>
       </c>
-      <c r="P139" s="1">
+      <c r="P139" s="7">
         <v>54.372419649999998</v>
       </c>
     </row>
@@ -16379,10 +16697,10 @@
       <c r="B140" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C140" s="1">
+      <c r="C140" s="7">
         <v>63.848999999999997</v>
       </c>
-      <c r="D140" s="1">
+      <c r="D140" s="7">
         <v>18.14</v>
       </c>
       <c r="E140" s="1" t="s">
@@ -16418,7 +16736,7 @@
       <c r="O140" s="3">
         <v>40786</v>
       </c>
-      <c r="P140" s="1">
+      <c r="P140" s="7">
         <v>84.911898260000001</v>
       </c>
     </row>
@@ -16429,10 +16747,10 @@
       <c r="B141" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C141" s="1">
+      <c r="C141" s="7">
         <v>33.268999999999998</v>
       </c>
-      <c r="D141" s="1">
+      <c r="D141" s="7">
         <v>15.445</v>
       </c>
       <c r="E141" s="1" t="s">
@@ -16468,7 +16786,7 @@
       <c r="O141" s="3">
         <v>41272</v>
       </c>
-      <c r="P141" s="1">
+      <c r="P141" s="7">
         <v>56.496030339999997</v>
       </c>
     </row>
@@ -16479,10 +16797,10 @@
       <c r="B142" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C142" s="1">
+      <c r="C142" s="7">
         <v>84.087000000000003</v>
       </c>
-      <c r="D142" s="1">
+      <c r="D142" s="7">
         <v>9.5749999999999993</v>
       </c>
       <c r="E142" s="1" t="s">
@@ -16518,7 +16836,7 @@
       <c r="O142" s="3">
         <v>40756</v>
       </c>
-      <c r="P142" s="1">
+      <c r="P142" s="7">
         <v>55.297116580000001</v>
       </c>
     </row>
@@ -16529,10 +16847,13 @@
       <c r="B143" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C143" s="1">
+      <c r="C143" s="7">
         <v>65.119</v>
       </c>
-      <c r="D143" s="5"/>
+      <c r="D143" s="11">
+        <f>Car_sales_Cleaned!D136</f>
+        <v>17.805</v>
+      </c>
       <c r="E143" s="1" t="s">
         <v>41</v>
       </c>
@@ -16566,7 +16887,7 @@
       <c r="O143" s="3">
         <v>41187</v>
       </c>
-      <c r="P143" s="1">
+      <c r="P143" s="7">
         <v>78.027219470000006</v>
       </c>
     </row>
@@ -16577,10 +16898,10 @@
       <c r="B144" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C144" s="1">
+      <c r="C144" s="7">
         <v>25.106000000000002</v>
       </c>
-      <c r="D144" s="1">
+      <c r="D144" s="7">
         <v>13.324999999999999</v>
       </c>
       <c r="E144" s="1" t="s">
@@ -16616,7 +16937,7 @@
       <c r="O144" s="3">
         <v>40669</v>
       </c>
-      <c r="P144" s="1">
+      <c r="P144" s="7">
         <v>51.955108869999997</v>
       </c>
     </row>
@@ -16627,10 +16948,10 @@
       <c r="B145" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C145" s="1">
+      <c r="C145" s="7">
         <v>68.411000000000001</v>
       </c>
-      <c r="D145" s="1">
+      <c r="D145" s="7">
         <v>19.425000000000001</v>
       </c>
       <c r="E145" s="1" t="s">
@@ -16666,7 +16987,7 @@
       <c r="O145" s="3">
         <v>40609</v>
       </c>
-      <c r="P145" s="1">
+      <c r="P145" s="7">
         <v>62.35557713</v>
       </c>
     </row>
@@ -16677,10 +16998,10 @@
       <c r="B146" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C146" s="1">
+      <c r="C146" s="7">
         <v>9.8350000000000009</v>
       </c>
-      <c r="D146" s="1">
+      <c r="D146" s="7">
         <v>34.08</v>
       </c>
       <c r="E146" s="1" t="s">
@@ -16716,7 +17037,7 @@
       <c r="O146" s="3">
         <v>40811</v>
       </c>
-      <c r="P146" s="1">
+      <c r="P146" s="7">
         <v>102.5289842</v>
       </c>
     </row>
@@ -16727,10 +17048,10 @@
       <c r="B147" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C147" s="1">
+      <c r="C147" s="7">
         <v>9.7609999999999992</v>
       </c>
-      <c r="D147" s="1">
+      <c r="D147" s="7">
         <v>11.425000000000001</v>
       </c>
       <c r="E147" s="1" t="s">
@@ -16766,7 +17087,7 @@
       <c r="O147" s="3">
         <v>40567</v>
       </c>
-      <c r="P147" s="1">
+      <c r="P147" s="7">
         <v>46.943876760000002</v>
       </c>
     </row>
@@ -16777,10 +17098,10 @@
       <c r="B148" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C148" s="1">
+      <c r="C148" s="7">
         <v>83.721000000000004</v>
       </c>
-      <c r="D148" s="1">
+      <c r="D148" s="7">
         <v>13.24</v>
       </c>
       <c r="E148" s="1" t="s">
@@ -16816,7 +17137,7 @@
       <c r="O148" s="3">
         <v>40782</v>
       </c>
-      <c r="P148" s="1">
+      <c r="P148" s="7">
         <v>47.638236659999997</v>
       </c>
     </row>
@@ -16827,10 +17148,10 @@
       <c r="B149" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C149" s="1">
+      <c r="C149" s="7">
         <v>51.101999999999997</v>
       </c>
-      <c r="D149" s="1">
+      <c r="D149" s="7">
         <v>16.725000000000001</v>
       </c>
       <c r="E149" s="1" t="s">
@@ -16866,7 +17187,7 @@
       <c r="O149" s="3">
         <v>41212</v>
       </c>
-      <c r="P149" s="1">
+      <c r="P149" s="7">
         <v>61.701381359999999</v>
       </c>
     </row>
@@ -16877,10 +17198,10 @@
       <c r="B150" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C150" s="1">
+      <c r="C150" s="7">
         <v>9.5690000000000008</v>
       </c>
-      <c r="D150" s="1">
+      <c r="D150" s="7">
         <v>16.574999999999999</v>
       </c>
       <c r="E150" s="1" t="s">
@@ -16916,7 +17237,7 @@
       <c r="O150" s="3">
         <v>40694</v>
       </c>
-      <c r="P150" s="1">
+      <c r="P150" s="7">
         <v>48.907372250000002</v>
       </c>
     </row>
@@ -16927,10 +17248,10 @@
       <c r="B151" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C151" s="1">
+      <c r="C151" s="7">
         <v>5.5960000000000001</v>
       </c>
-      <c r="D151" s="1">
+      <c r="D151" s="7">
         <v>13.76</v>
       </c>
       <c r="E151" s="1" t="s">
@@ -16966,7 +17287,7 @@
       <c r="O151" s="3">
         <v>40634</v>
       </c>
-      <c r="P151" s="1">
+      <c r="P151" s="7">
         <v>47.946841059999997</v>
       </c>
     </row>
@@ -16977,10 +17298,13 @@
       <c r="B152" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C152" s="1">
+      <c r="C152" s="7">
         <v>49.463000000000001</v>
       </c>
-      <c r="D152" s="5"/>
+      <c r="D152" s="11">
+        <f>Car_sales_Cleaned!D145</f>
+        <v>19.425000000000001</v>
+      </c>
       <c r="E152" s="1" t="s">
         <v>18</v>
       </c>
@@ -17014,7 +17338,7 @@
       <c r="O152" s="3">
         <v>40836</v>
       </c>
-      <c r="P152" s="1">
+      <c r="P152" s="7">
         <v>47.329632259999997</v>
       </c>
     </row>
@@ -17025,10 +17349,13 @@
       <c r="B153" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C153" s="1">
+      <c r="C153" s="7">
         <v>16.957000000000001</v>
       </c>
-      <c r="D153" s="5"/>
+      <c r="D153" s="11">
+        <f>Car_sales_Cleaned!D146</f>
+        <v>34.08</v>
+      </c>
       <c r="E153" s="1" t="s">
         <v>18</v>
       </c>
@@ -17062,7 +17389,7 @@
       <c r="O153" s="3">
         <v>40592</v>
       </c>
-      <c r="P153" s="1">
+      <c r="P153" s="7">
         <v>66.113056799999995</v>
       </c>
     </row>
@@ -17073,10 +17400,13 @@
       <c r="B154" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C154" s="1">
+      <c r="C154" s="7">
         <v>3.5449999999999999</v>
       </c>
-      <c r="D154" s="5"/>
+      <c r="D154" s="11">
+        <f>Car_sales_Cleaned!D147</f>
+        <v>11.425000000000001</v>
+      </c>
       <c r="E154" s="1" t="s">
         <v>18</v>
       </c>
@@ -17110,7 +17440,7 @@
       <c r="O154" s="3">
         <v>40807</v>
       </c>
-      <c r="P154" s="1">
+      <c r="P154" s="7">
         <v>66.498812299999997</v>
       </c>
     </row>
@@ -17121,10 +17451,13 @@
       <c r="B155" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C155" s="1">
+      <c r="C155" s="7">
         <v>15.244999999999999</v>
       </c>
-      <c r="D155" s="5"/>
+      <c r="D155" s="11">
+        <f>Car_sales_Cleaned!D148</f>
+        <v>13.24</v>
+      </c>
       <c r="E155" s="1" t="s">
         <v>18</v>
       </c>
@@ -17158,7 +17491,7 @@
       <c r="O155" s="3">
         <v>41237</v>
       </c>
-      <c r="P155" s="1">
+      <c r="P155" s="7">
         <v>70.654495449999999</v>
       </c>
     </row>
@@ -17169,10 +17502,13 @@
       <c r="B156" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C156" s="1">
+      <c r="C156" s="7">
         <v>17.530999999999999</v>
       </c>
-      <c r="D156" s="5"/>
+      <c r="D156" s="11">
+        <f>Car_sales_Cleaned!D149</f>
+        <v>16.725000000000001</v>
+      </c>
       <c r="E156" s="1" t="s">
         <v>18</v>
       </c>
@@ -17206,7 +17542,7 @@
       <c r="O156" s="3">
         <v>40719</v>
       </c>
-      <c r="P156" s="1">
+      <c r="P156" s="7">
         <v>71.1559776</v>
       </c>
     </row>
@@ -17217,10 +17553,13 @@
       <c r="B157" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C157" s="1">
+      <c r="C157" s="7">
         <v>3.4929999999999999</v>
       </c>
-      <c r="D157" s="5"/>
+      <c r="D157" s="11">
+        <f>Car_sales_Cleaned!D150</f>
+        <v>16.574999999999999</v>
+      </c>
       <c r="E157" s="1" t="s">
         <v>18</v>
       </c>
@@ -17254,7 +17593,7 @@
       <c r="O157" s="3">
         <v>40659</v>
       </c>
-      <c r="P157" s="1">
+      <c r="P157" s="7">
         <v>101.6233572</v>
       </c>
     </row>
@@ -17265,10 +17604,13 @@
       <c r="B158" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C158" s="1">
+      <c r="C158" s="7">
         <v>18.969000000000001</v>
       </c>
-      <c r="D158" s="5"/>
+      <c r="D158" s="11">
+        <f>Car_sales_Cleaned!D151</f>
+        <v>13.76</v>
+      </c>
       <c r="E158" s="1" t="s">
         <v>18</v>
       </c>
@@ -17302,7 +17644,7 @@
       <c r="O158" s="3">
         <v>40861</v>
       </c>
-      <c r="P158" s="1">
+      <c r="P158" s="7">
         <v>85.735654510000003</v>
       </c>
     </row>
@@ -17311,4 +17653,216 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65068E26-3889-401B-BA0C-7D8197D1B33B}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="6">
+        <v>36</v>
+      </c>
+      <c r="C2" s="12">
+        <v>18.072975206611574</v>
+      </c>
+      <c r="D2" s="8">
+        <v>14.18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12">
+        <v>27.390754838709661</v>
+      </c>
+      <c r="D3" s="12">
+        <v>22.798999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="12">
+        <v>3.0608974358974339</v>
+      </c>
+      <c r="D4" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="12">
+        <v>185.94871794871796</v>
+      </c>
+      <c r="D5" s="8">
+        <v>177.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12">
+        <v>107.48717948717949</v>
+      </c>
+      <c r="D6" s="8">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8">
+        <v>71.149999999999963</v>
+      </c>
+      <c r="D7" s="8">
+        <v>70.55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="12">
+        <v>187.34358974358977</v>
+      </c>
+      <c r="D8" s="8">
+        <v>187.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="6">
+        <v>2</v>
+      </c>
+      <c r="C9" s="12">
+        <v>3.3780258064516131</v>
+      </c>
+      <c r="D9" s="8">
+        <v>3.3420000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="12">
+        <v>17.951923076923084</v>
+      </c>
+      <c r="D10" s="8">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="6">
+        <v>3</v>
+      </c>
+      <c r="C11" s="12">
+        <v>23.844155844155843</v>
+      </c>
+      <c r="D11" s="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="6">
+        <v>0</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="6">
+        <v>2</v>
+      </c>
+      <c r="C13" s="12">
+        <v>77.043591200774202</v>
+      </c>
+      <c r="D13" s="12">
+        <v>72.030917189999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="8">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>